--- a/data/prospects.xlsx
+++ b/data/prospects.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q101"/>
+  <dimension ref="A1:Q221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -8551,6 +8551,9402 @@
         </is>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>B-registre à qualifier</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Luc Flores</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Dirigeant de plusieurs sociétés (Cadrinvest TP; Sesmar; LFTB)</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Cadrinvest TP / Haras des Pyrénées</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Pyrénées</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.pappers.fr/dirigeant/luc_flores_1973-02</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Cumul de mandats : Haras des Pyrénées + sociétés BTP/holding</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>Fiche dirigeant Pappers : gérant/président de plusieurs SAS-SARL dont le Haras des Pyrénées</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>https://www.pappers.fr/dirigeant/luc_flores_1973-02</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>proprietaire_chevaux</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>haras</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>B-registre à qualifier</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Emmanuel Boutin</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Dirigeant (SPFPL; probable vétérinaire équin)</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Écurie Vivaldi Rock / Haras de Livet</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Normandie</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.pappers.fr/dirigeant/emmanuel_boutin_1977-05</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Cumul de mandats : écurie + haras + structure d'exercice libéral</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>Fiche dirigeant Pappers : Écurie Vivaldi Rock, Haras de Livet, SPFPL vétérinaire équine</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>https://www.pappers.fr/dirigeant/emmanuel_boutin_1977-05</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>proprietaire_chevaux</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>haras</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>B-registre à qualifier</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Gonzague Arnoulx de Pirey</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Dirigeant de holding familiale</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Holding Familiale Pirey / SARL Haras du Bailly</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.pappers.fr/dirigeant/gonzague_arnoulx%20de%20pirey_1974-11</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Cumul de mandats : holding familiale + haras</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>Fiche dirigeant Pappers : Holding Familiale Pirey + SARL Haras du Bailly</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>https://www.pappers.fr/dirigeant/gonzague_arnoulx%20de%20pirey_1974-11</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>proprietaire_chevaux</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>haras</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>B-registre à qualifier</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Jérôme Bruet</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Dirigeant</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>JKB / Haras de Nantes Académie / Haras de la Vaillantière</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Nantes</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.pappers.fr/dirigeant/jerome_bruet_1973-11</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Cumul de mandats : société JKB + deux structures haras</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>Fiche dirigeant Pappers : gérant de JKB, Haras de Nantes Académie, Haras de la Vaillantière</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>https://www.pappers.fr/dirigeant/jerome_bruet_1973-11</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>proprietaire_chevaux</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>haras</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>B-registre à qualifier</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Luis Do Souto</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Dirigeant</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Aquitaine Bureau</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Aquitaine</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.pappers.fr/dirigeant/luis_do%20souto_1973-02</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Fiche dirigeant remontée sur requête « haras » (lien à confirmer)</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>Fiche dirigeant Pappers remontée sur requête haras + président/gérant</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>https://www.pappers.fr/dirigeant/luis_do%20souto_1973-02</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>proprietaire_chevaux</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>haras</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>B-à qualifier (presse)</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Michel Bouvier</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Président de la Société des Courses de Pornichet (profession à confirmer)</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Société des Courses de Pornichet</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Pornichet (44)</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Michel%20Bouvier%20Pornichet</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Président bénévole d'hippodrome (passion courses prouvée)</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>Réélu président à l'unanimité (site officiel de l'hippodrome)</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>https://www.hippodrome-pornichet.fr/actualites/michel-bouvier-reelu-president-lunanimite</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>aucun</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>B-à qualifier (presse)</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Claude Rouy</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Président de la Société des Courses d'Aix-les-Bains (profession à confirmer)</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Société des Courses d'Aix-les-Bains</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Aix-les-Bains (73)</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Claude%20Rouy%20Aix-les-Bains</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Président bénévole d'hippodrome</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>Élu président en 2024 (presse locale)</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>https://www.ballad-et-vous.fr/actualites/savoie-un-nouveau-president-a-la-societe-des-courses-daix-les-bains/</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>aucun</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>B-à qualifier (presse)</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>François-Xavier Duny</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Président de la Société des Courses de Pompadour (profession à confirmer)</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Société des Courses de Pompadour</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Arnac-Pompadour (19)</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Fran%C3%A7ois-Xavier%20Duny</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Président bénévole d'hippodrome</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>Président de la société des courses (site officiel)</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>https://courses-pompadour.fr/?page_id=6388</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>aucun</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>B-à qualifier (presse)</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Hervé de Villette</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Président de la Société des Courses de Paray-le-Monial (profession à confirmer)</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Société des Courses de Paray-le-Monial</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Paray-le-Monial (71)</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Herv%C3%A9%20de%20Villette</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Président bénévole d'hippodrome + programme de modernisation</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>Président, a engagé la modernisation de l'hippodrome (site officiel)</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>https://www.hippodrome-paraylemonial.com/la-societe-des-courses/</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>aucun</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>B-à qualifier (presse)</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Gérard Gordat</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Vice-président de la Société des Courses de Paray-le-Monial (15 ans)</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Société des Courses de Paray-le-Monial</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Paray-le-Monial (71)</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=G%C3%A9rard%20Gordat</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Vice-président bénévole d'hippodrome</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>Préside le conseil d'administration depuis plus de 15 ans (site officiel)</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>https://www.hippodrome-paraylemonial.com/la-societe-des-courses/</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>aucun</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr"/>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>A-presse</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Manuel Demnard</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Ex-chef d'entreprise; président de l'association des courses de Toulouse</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Association sportive des courses de Toulouse (La Cépière)</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Toulouse (31)</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Manuel%20Demnard</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Ancien chef d'entreprise devenu président d'hippodrome (500 K EUR investis)</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>Élu président en juin 2023, ancien chef d'entreprise (Gazette du Midi)</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>https://gazette-du-midi.fr/au-sommaire/entreprises/l-hippodrome-de-toulouse-la-cepiere</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>aucun</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>B-à qualifier (presse)</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Jean-Pierre Thomain</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Président de l'hippodrome de Graignes (monde agricole)</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Hippodrome de Graignes</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Graignes (50)</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Jean-Pierre%20Thomain</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Président d'hippodrome; 20 ans d'engagement bénévole dans les courses</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>À la tête de l'hippodrome depuis 2023, issu du monde agricole (FNCH)</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>https://www.fnch.fr/national/actualit%C3%A9s/lhippodrome-du-mois-20</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>aucun</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>B-profil LinkedIn à qualifier</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Julie André</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Front Office Manager (hôtellerie)</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/julie-andre-b90a35157</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Galop 7 d'équitation affiché sur le profil (diplôme 2010)</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>Profil LinkedIn mentionnant le Galop 7 (requête site:linkedin "galop 7" + manager)</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/julie-andre-b90a35157</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>incertain</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>affinite_cheval</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>mention équestre générique</t>
+        </is>
+      </c>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>18.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>B-profil LinkedIn à qualifier</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Gabrielle Guallar</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Responsable Affaires Publiques (Secrétariat général)</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>LVMH</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/gabrielle-guallar-a2b9b025</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Profil remonté sur requête « galop 7 » + responsable</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>Requête Google site:linkedin "galop 7" + responsable; indice à confirmer</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/gabrielle-guallar-a2b9b025</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>aucun</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q115" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>B-profil LinkedIn à qualifier</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Alexis Perrin</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Consultant / associé</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Abelya Partners</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/perrinalexis/en</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Profil remonté sur requête « galop 7 » + fondateur/manager</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>Requête Google site:linkedin "galop 7"; indice à confirmer</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/perrinalexis/en</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>aucun</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>B-profil LinkedIn à qualifier</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Jean-Baptiste Chauvel</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Cadre</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Maxi Zoo France</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/jean-baptiste-chauvel-132006132</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Profil remonté sur requête « passionné de chevaux » + responsable</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>Requête Google "passionné de chevaux" + directeur/responsable</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/jean-baptiste-chauvel-132006132</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>incertain</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>affinite_cheval</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>mention équestre générique</t>
+        </is>
+      </c>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="Q117" t="inlineStr">
+        <is>
+          <t>14.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>B-profil LinkedIn à qualifier</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Gaëlle Baucheron</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Cadre</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Caen (14)</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/ga%C3%ABlle-baucheron-1a4aaa145</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Profil remonté sur requête « passionnée de chevaux »</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>Requête Google "passionnée de chevaux" + directeur/responsable</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/ga%C3%ABlle-baucheron-1a4aaa145</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>incertain</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>affinite_cheval</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>mention équestre générique</t>
+        </is>
+      </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>14.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>B-profil LinkedIn à qualifier</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Zoé Jossart</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Chargée de missions événementielles</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Événementiel (équestre)</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/zo%C3%A9-jossart</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Profil remonté deux fois sur des requêtes équestres distinctes</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>Requêtes Google "passionnée de chevaux" et "concours d'équitation"</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/zo%C3%A9-jossart</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>incertain</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>affinite_cheval</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>mention équestre générique</t>
+        </is>
+      </c>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>B-profil LinkedIn à qualifier</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Narimane Langlois</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Fondatrice</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>MANAM Design</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/narimane-langlois</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Profil remonté sur requête « passion équestre » + fondatrice</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>Requête Google "passion équestre"/"sports équestres" + fondatrice</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/narimane-langlois</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>aucun</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr"/>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>B-profil LinkedIn à qualifier</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Émilie Prudence</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Dirigeante</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Phoenix Evènements</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/%C3%A9milie-prudence-phoenix</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Profil remonté sur requête « passion équestre » + dirigeante</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>Requête Google "passion équestre" + dirigeante</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/%C3%A9milie-prudence-phoenix</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>aucun</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr"/>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>B-profil LinkedIn à qualifier</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Cindy Girerd</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Fondatrice</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Com' Killer</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/cindy-girerd</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Profil remonté sur requête « passion équestre » + fondatrice (événementiel sportif)</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>Requête Google "passion équestre" + fondatrice</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/cindy-girerd</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>aucun</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr"/>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>B-profil LinkedIn à qualifier</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Emmeline Lambard</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Fondatrice - Dirigeante</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/emmeline-lambard-14018a273</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Profil remonté sur requête « passion équestre » + fondatrice/dirigeante</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>Requête Google "passion équestre" + dirigeante</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/emmeline-lambard-14018a273</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>aucun</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr"/>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>B-profil LinkedIn à qualifier</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>François Singer</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Directeur Général</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Sportmed Summit / sport business</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/fran%C3%A7ois-singer-8b06722b</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Profil remonté sur requête « sports équestres » + directeur</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>Requête Google "sports équestres" + directeur</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/fran%C3%A7ois-singer-8b06722b</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>aucun</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr"/>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q124" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>B-profil LinkedIn à qualifier</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Lucile Sachot</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Cadre</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Chambre d'Agriculture de la Lozère</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Lozère</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/lucile-sachot-128a31178</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Profil remonté sur requête « passion équestre » + responsable</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>Requête Google "passion équestre" + responsable</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/lucile-sachot-128a31178</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>aucun</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr"/>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q125" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>B-à qualifier (association)</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Jean-Jacques Barre</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Membre du comité national UNAT (profession à confirmer)</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>UNAT - Union Nationale des Amateurs de Trot</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr"/>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Jean-Jacques%20Barre</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Amateur de trot (drive/possède des trotteurs) - membre du comité national UNAT</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>Liste officielle du comité national UNAT (unat.fr/unat-administration)</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>https://unat.fr/unat-administration/</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>proprietaire_chevaux</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>trotteur</t>
+        </is>
+      </c>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="Q126" t="inlineStr">
+        <is>
+          <t>27.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>B-à qualifier (association)</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Jean-Philippe Bazire</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Président UNAT Normandie (profession à confirmer)</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>UNAT - Union Nationale des Amateurs de Trot</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr"/>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Jean-Philippe%20Bazire</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Amateur de trot (drive/possède des trotteurs) - membre du comité national UNAT</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>Liste officielle du comité national UNAT (unat.fr/unat-administration)</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>https://unat.fr/unat-administration/</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>proprietaire_chevaux</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>trotteur</t>
+        </is>
+      </c>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="Q127" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>B-à qualifier (association)</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Pascal Boey</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Président UNAT Île-de-France Nord et Est (profession à confirmer)</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>UNAT - Union Nationale des Amateurs de Trot</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr"/>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Pascal%20Boey</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Amateur de trot (drive/possède des trotteurs) - membre du comité national UNAT</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>Liste officielle du comité national UNAT (unat.fr/unat-administration)</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>https://unat.fr/unat-administration/</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>proprietaire_chevaux</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>trotteur</t>
+        </is>
+      </c>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="Q128" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>B-à qualifier (association)</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Jean-Jacques Bouquet</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Membre du comité national UNAT (profession à confirmer)</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>UNAT - Union Nationale des Amateurs de Trot</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Jean-Jacques%20Bouquet</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Amateur de trot (drive/possède des trotteurs) - membre du comité national UNAT</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>Liste officielle du comité national UNAT (unat.fr/unat-administration)</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>https://unat.fr/unat-administration/</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>proprietaire_chevaux</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>trotteur</t>
+        </is>
+      </c>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="Q129" t="inlineStr">
+        <is>
+          <t>27.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>B-à qualifier (association)</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Patrick Carmoy</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Membre du comité national UNAT (profession à confirmer)</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>UNAT - Union Nationale des Amateurs de Trot</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Patrick%20Carmoy</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Amateur de trot (drive/possède des trotteurs) - membre du comité national UNAT</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>Liste officielle du comité national UNAT (unat.fr/unat-administration)</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>https://unat.fr/unat-administration/</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>proprietaire_chevaux</t>
+        </is>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>trotteur</t>
+        </is>
+      </c>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="Q130" t="inlineStr">
+        <is>
+          <t>27.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>B-à qualifier (association)</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Frédéric Durville</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Membre du comité national UNAT (profession à confirmer)</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>UNAT - Union Nationale des Amateurs de Trot</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr"/>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Frédéric%20Durville</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Amateur de trot (drive/possède des trotteurs) - membre du comité national UNAT</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>Liste officielle du comité national UNAT (unat.fr/unat-administration)</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>https://unat.fr/unat-administration/</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>proprietaire_chevaux</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>trotteur</t>
+        </is>
+      </c>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="Q131" t="inlineStr">
+        <is>
+          <t>27.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>B-à qualifier (association)</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Pierre-Loup Devouassoux</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Membre du comité national UNAT (profession à confirmer)</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>UNAT - Union Nationale des Amateurs de Trot</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr"/>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Pierre-Loup%20Devouassoux</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>Amateur de trot (drive/possède des trotteurs) - membre du comité national UNAT</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>Liste officielle du comité national UNAT (unat.fr/unat-administration)</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>https://unat.fr/unat-administration/</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>proprietaire_chevaux</t>
+        </is>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>trotteur</t>
+        </is>
+      </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="Q132" t="inlineStr">
+        <is>
+          <t>27.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>B-à qualifier (association)</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Jean-Michel Empeytaz</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Membre du comité national UNAT (profession à confirmer)</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>UNAT - Union Nationale des Amateurs de Trot</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Jean-Michel%20Empeytaz</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>Amateur de trot (drive/possède des trotteurs) - membre du comité national UNAT</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>Liste officielle du comité national UNAT (unat.fr/unat-administration)</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>https://unat.fr/unat-administration/</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>proprietaire_chevaux</t>
+        </is>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>trotteur</t>
+        </is>
+      </c>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="Q133" t="inlineStr">
+        <is>
+          <t>27.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>B-à qualifier (association)</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Benoît Fedry</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Membre du comité national UNAT (profession à confirmer)</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>UNAT - Union Nationale des Amateurs de Trot</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Benoît%20Fedry</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>Amateur de trot (drive/possède des trotteurs) - membre du comité national UNAT</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>Liste officielle du comité national UNAT (unat.fr/unat-administration)</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>https://unat.fr/unat-administration/</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>proprietaire_chevaux</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>trotteur</t>
+        </is>
+      </c>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="Q134" t="inlineStr">
+        <is>
+          <t>27.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>B-à qualifier (association)</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Hubert Jay</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Président UNAT Centre-Est (profession à confirmer)</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>UNAT - Union Nationale des Amateurs de Trot</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Hubert%20Jay</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Amateur de trot (drive/possède des trotteurs) - membre du comité national UNAT</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>Liste officielle du comité national UNAT (unat.fr/unat-administration)</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>https://unat.fr/unat-administration/</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>proprietaire_chevaux</t>
+        </is>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>trotteur</t>
+        </is>
+      </c>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="Q135" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>B-à qualifier (association)</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Jean-Claude Louche</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Membre du comité national UNAT (profession à confirmer)</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>UNAT - Union Nationale des Amateurs de Trot</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr"/>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Jean-Claude%20Louche</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>Amateur de trot (drive/possède des trotteurs) - membre du comité national UNAT</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>Liste officielle du comité national UNAT (unat.fr/unat-administration)</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>https://unat.fr/unat-administration/</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>proprietaire_chevaux</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>trotteur</t>
+        </is>
+      </c>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="Q136" t="inlineStr">
+        <is>
+          <t>27.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>B-à qualifier (association)</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Dorice Mulot</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Membre du comité national UNAT (profession à confirmer)</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>UNAT - Union Nationale des Amateurs de Trot</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr"/>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Dorice%20Mulot</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>Amateur de trot (drive/possède des trotteurs) - membre du comité national UNAT</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>Liste officielle du comité national UNAT (unat.fr/unat-administration)</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>https://unat.fr/unat-administration/</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>proprietaire_chevaux</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>trotteur</t>
+        </is>
+      </c>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="Q137" t="inlineStr">
+        <is>
+          <t>27.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>B-à qualifier (association)</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Bernard Pellan</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Président UNAT Ouest/Anjou-Maine (profession à confirmer)</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>UNAT - Union Nationale des Amateurs de Trot</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr"/>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Bernard%20Pellan</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Amateur de trot (drive/possède des trotteurs) - membre du comité national UNAT</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>Liste officielle du comité national UNAT (unat.fr/unat-administration)</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>https://unat.fr/unat-administration/</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>proprietaire_chevaux</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>trotteur</t>
+        </is>
+      </c>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="Q138" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>B-à qualifier (association)</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Éric Perekrestoff</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Président UNAT Sud-Ouest (profession à confirmer)</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>UNAT - Union Nationale des Amateurs de Trot</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr"/>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Éric%20Perekrestoff</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Amateur de trot (drive/possède des trotteurs) - membre du comité national UNAT</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>Liste officielle du comité national UNAT (unat.fr/unat-administration)</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>https://unat.fr/unat-administration/</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>proprietaire_chevaux</t>
+        </is>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>trotteur</t>
+        </is>
+      </c>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="Q139" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>B-à qualifier (association)</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Patrick Polizzi</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Président UNAT Sud-Est (profession à confirmer)</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>UNAT - Union Nationale des Amateurs de Trot</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Patrick%20Polizzi</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>Amateur de trot (drive/possède des trotteurs) - membre du comité national UNAT</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>Liste officielle du comité national UNAT (unat.fr/unat-administration)</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>https://unat.fr/unat-administration/</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>proprietaire_chevaux</t>
+        </is>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>trotteur</t>
+        </is>
+      </c>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="Q140" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>B-à qualifier (association)</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Alfred Trouvé</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Membre du comité national UNAT (profession à confirmer)</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>UNAT - Union Nationale des Amateurs de Trot</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Alfred%20Trouvé</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr"/>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>Amateur de trot (drive/possède des trotteurs) - membre du comité national UNAT</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>Liste officielle du comité national UNAT (unat.fr/unat-administration)</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>https://unat.fr/unat-administration/</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>proprietaire_chevaux</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>trotteur</t>
+        </is>
+      </c>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="Q141" t="inlineStr">
+        <is>
+          <t>27.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>A-presse</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Guy d'Arexy</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Fondateur</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Agence Globale</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Guy%20d'Arexy</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>Ex-gentleman-rider, fondateur de l'Agence Globale, membre du bureau du Club GRC</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>Nouveau membre du bureau : ancien gentleman-rider et fondateur de l'Agence Globale (Jour de Galop)</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>https://www.jourdegalop.com/2023/05/le-club-des-gentlemen-demenage-et-elit-son-bureau/</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>aucun</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr"/>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q142" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>A-presse</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Georges-Alexandre Ancenys</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Dirigeant du fonds d'investissement SPE Capital</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>SPE Capital</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Georges-Alexandre%20Ancenys</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>Membre du bureau du Club des Gentlemen-Riders (cavalier de courses amateur)</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>Nouveau membre du bureau : à la tête du fonds d'investissement SPE Capital (Jour de Galop)</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>https://www.jourdegalop.com/2023/05/le-club-des-gentlemen-demenage-et-elit-son-bureau/</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>aucun</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr"/>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q143" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>B-à qualifier (association)</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Paul-Henri de Quatrebarbes</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Président du Club des Gentlemen-Riders (profession à confirmer)</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Club GRC</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Paul-Henri%20de%20Quatrebarbes</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Gentleman-rider, président du Club GRC</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>Élu président du Club des Gentlemen-Riders et des Cavalières (Equidia)</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>https://www.equidia.fr/articles/actualite/paul-henri-de-quatrebarbes-nouveau-president-du-club-des-gentlemen-riders-et-des-cavalieres-de-france</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>aucun</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr"/>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q144" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>B-à qualifier (association)</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Jean-Philippe Boisgontier</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Vice-président du Club GRC (profession à confirmer)</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Club GRC</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Jean-Philippe%20Boisgontier</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>Gentleman-rider, vice-président du Club GRC</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>Bureau du Club GRC (Jour de Galop)</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>https://www.jourdegalop.com/2023/05/le-club-des-gentlemen-demenage-et-elit-son-bureau/</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>aucun</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr"/>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q145" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>B-à qualifier (association)</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Patrice Détré</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Vice-président du Club GRC (profession à confirmer)</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Club GRC</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Patrice%20Détré</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>Gentleman-rider, vice-président du Club GRC</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>Bureau du Club GRC (Jour de Galop)</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>https://www.jourdegalop.com/2023/05/le-club-des-gentlemen-demenage-et-elit-son-bureau/</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>aucun</t>
+        </is>
+      </c>
+      <c r="O146" t="inlineStr"/>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q146" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>B-à qualifier (association)</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Gérard de Chevigny</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Ex-président du Club GRC - 4 mandats (profession à confirmer)</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Club GRC</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Gérard%20de%20Chevigny</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Gentleman-rider, ancien président du Club GRC</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>A achevé son 4e mandat de président (Equidia)</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>https://www.equidia.fr/articles/actualite/paul-henri-de-quatrebarbes-nouveau-president-du-club-des-gentlemen-riders-et-des-cavalieres-de-france</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>aucun</t>
+        </is>
+      </c>
+      <c r="O147" t="inlineStr"/>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q147" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>B-profil LinkedIn à qualifier</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Maurice Cohen</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Chef d'entreprise (transports T.M.C)</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Transports T.M.C</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/maurice-cohen-4147a037</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Indice équestre détecté via requête Google croisée (à confirmer sur le profil)</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>Profil remonté sur requête « propriétaire » + « cheval de course » + dirigeant</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/maurice-cohen-4147a037</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>incertain</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>affinite_cheval</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>mention équestre générique</t>
+        </is>
+      </c>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t>17.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>B-profil LinkedIn à qualifier</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Justin De Carvalho</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Co-fondateur</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Second Souffle</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/justin-de-carvalho-bb5547209</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr"/>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Indice équestre détecté via requête Google croisée (à confirmer sur le profil)</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>Profil remonté sur requête « propriétaire cheval de course/trotteur » + fondateur</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/justin-de-carvalho-bb5547209</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>proprietaire_chevaux</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>trotteur</t>
+        </is>
+      </c>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="Q149" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>B-profil LinkedIn à qualifier</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Lionel Martinez</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Fondateur</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Territoire Studio</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/martinez-lionel</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr"/>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Indice équestre détecté via requête Google croisée (à confirmer sur le profil)</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>Profil remonté sur requête « propriétaire cheval de course/trotteur » + fondateur</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/martinez-lionel</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>proprietaire_chevaux</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>trotteur</t>
+        </is>
+      </c>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="Q150" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>B-profil LinkedIn à qualifier</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Patrick Lechat</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Dirigeant</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>PluService Propreté &amp; Parquet</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/patrick-lechat-649352176</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr"/>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>Indice équestre détecté via requête Google croisée (à confirmer sur le profil)</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>Profil remonté sur requête « propriétaire cheval de course/trotteur »</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/patrick-lechat-649352176</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>proprietaire_chevaux</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>trotteur</t>
+        </is>
+      </c>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="Q151" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>B-profil LinkedIn à qualifier</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Jonathan Deveze</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Dirigeant</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Bedrich Hydrants</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/jonathan-deveze</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr"/>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Indice équestre détecté via requête Google croisée (à confirmer sur le profil)</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>Profil remonté sur requête « propriétaire cheval de course/trotteur »</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/jonathan-deveze</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>proprietaire_chevaux</t>
+        </is>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>trotteur</t>
+        </is>
+      </c>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="Q152" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>B-profil LinkedIn à qualifier</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>François de Rouffignac</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>DRH (hôtellerie-restauration)</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr"/>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/fran%C3%A7ois-de-rouffignac-53832427</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr"/>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>Indice équestre détecté via requête Google croisée (à confirmer sur le profil)</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>Profil remonté sur requête « cavalière/cavalier » + ressources humaines</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/fran%C3%A7ois-de-rouffignac-53832427</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>aucun</t>
+        </is>
+      </c>
+      <c r="O153" t="inlineStr"/>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>B-profil LinkedIn à qualifier</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Lou Froissardey</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Chargée des Ressources Humaines</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>ECM Besançon</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/lou-froissardey-754937221</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Indice équestre détecté via requête Google croisée (à confirmer sur le profil)</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>Profil remonté sur requête « cavalière » + ressources humaines</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/lou-froissardey-754937221</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>aucun</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr"/>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q154" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>B-profil LinkedIn à qualifier</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Élodie Dehen</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Cadre</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>ARESCOM (informatique)</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/elodie-dehen-252a72188</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr"/>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Indice équestre détecté via requête Google croisée (à confirmer sur le profil)</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>Profil remonté sur requête « cavalière » + recrutement</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/elodie-dehen-252a72188</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>aucun</t>
+        </is>
+      </c>
+      <c r="O155" t="inlineStr"/>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q155" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>B-profil LinkedIn à qualifier</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Adam-Aïcha Anne</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Cadre</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>BNP Paribas Personal Finance</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr"/>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/adam-a%C3%AFcha-anne</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr"/>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>Indice équestre détecté via requête Google croisée (à confirmer sur le profil)</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>Profil remonté sur requête « cavalière » + ressources humaines</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/adam-a%C3%AFcha-anne</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>aucun</t>
+        </is>
+      </c>
+      <c r="O156" t="inlineStr"/>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q156" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>B-profil LinkedIn à qualifier</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Chantal Laterrade</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Chargée de recrutement</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>FMS Entreprise Adaptée</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/chantal-laterrade-a4b12821b</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr"/>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Indice équestre détecté via requête Google croisée (à confirmer sur le profil)</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>Profil remonté sur requête « cavalière » + recrutement</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/chantal-laterrade-a4b12821b</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>aucun</t>
+        </is>
+      </c>
+      <c r="O157" t="inlineStr"/>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q157" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>A-presse (célébrité)</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Antoine Griezmann</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Footballeur international &amp; investisseur (esport, media)</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Écurie Griezmann (12 trotteurs)</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Antoine%20Griezmann</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr"/>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Propriétaire officiel de trotteurs depuis 2017 (casaque noire étoiles roses); conseillé par Pierre Pilarski</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>Fiche propriétaire officielle LeTrot; a revendu un cheval 1,2 M EUR</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>https://www.letrot.com/stats/homme/Ecurie-GRIEZMANN/bGJbZQIEeA/proprietaire</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>proprietaire_chevaux</t>
+        </is>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>trotteur</t>
+        </is>
+      </c>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="Q158" t="inlineStr">
+        <is>
+          <t>38.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>B-à qualifier (presse)</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Isabelle Lerenaudie</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Capitaine de l'équipe Barrière Polo Team (profession à confirmer)</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Barrière Polo Team</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr"/>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Isabelle%20Lerenaudie</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr"/>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Capitaine française victorieuse de la Coupe d'Or de Deauville 2023 (polo 16 goals)</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>Première victoire en 16 goals d'une capitaine française (Coupe d'Or 2023)</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>https://www.deauvillepoloclub.com/coupe-d-or-2023</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>cavalier_pratiquant</t>
+        </is>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>polo</t>
+        </is>
+      </c>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="Q159" t="inlineStr">
+        <is>
+          <t>35.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>B-à qualifier (presse)</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Arnaud de Seyssel</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Vice-président de France Galop (profession à confirmer)</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>France Galop</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Arnaud%20de%20Seyssel</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr"/>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Ex-président de la Société des Courses d'Aix-les-Bains, élu vice-président de France Galop</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>Élu à la vice-présidence de France Galop (presse locale, 2024)</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>https://www.ballad-et-vous.fr/actualites/savoie-un-nouveau-president-a-la-societe-des-courses-daix-les-bains/</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>proprietaire_chevaux</t>
+        </is>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>france galop</t>
+        </is>
+      </c>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="Q160" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>B-à qualifier (association)</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Alain Bohan</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Président d'un Comité Départemental d'Équitation (profession à confirmer)</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>CDE (FFE)</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr"/>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Alain%20Bohan</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr"/>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Président élu d'un comité départemental d'équitation (dirigeant bénévole de la filière)</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>Élu président du CDE à la majorité (site CDE/FFE)</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>https://cde44.com/comite-directeur</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>incertain</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>affinite_cheval</t>
+        </is>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>mention équestre générique</t>
+        </is>
+      </c>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="Q161" t="inlineStr">
+        <is>
+          <t>25.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>B-à qualifier (association)</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Jean de Cheffontaines</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Propriétaire élu au Comité de France Galop (Fédération des Propriétaires du Galop)</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>France Galop</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr"/>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Jean%20de%20Cheffontaines</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr"/>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Propriétaire de chevaux de galop, élu au Comité France Galop 2023</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>Résultats officiels des élections France Galop 2023</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>https://billetterie.france-galop.com/app/uploads/2023/11/CP-France-Galop-Nouvelle-composition-du-Comite-de-France-Galop-2023-1.pdf</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>proprietaire_chevaux</t>
+        </is>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>proprietaire de chevaux</t>
+        </is>
+      </c>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="Q162" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>B-à qualifier (association)</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Paul Couderc</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Propriétaire élu au Comité de France Galop (FPG)</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>France Galop</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr"/>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Paul%20Couderc</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr"/>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Propriétaire de galopeurs, élu au Comité 2023</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>Résultats officiels des élections France Galop 2023</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>https://billetterie.france-galop.com/app/uploads/2023/11/CP-France-Galop-Nouvelle-composition-du-Comite-de-France-Galop-2023-1.pdf</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>proprietaire_chevaux</t>
+        </is>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>galopeur</t>
+        </is>
+      </c>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="Q163" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>B-à qualifier (association)</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Guy-Charles Fanneau de La Horie</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Propriétaire élu au Comité de France Galop (AEPI)</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>France Galop</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr"/>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Guy-Charles%20Fanneau%20de%20La%20Horie</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr"/>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Propriétaire de galopeurs, élu au Comité 2023</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>Résultats officiels des élections France Galop 2023</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>https://billetterie.france-galop.com/app/uploads/2023/11/CP-France-Galop-Nouvelle-composition-du-Comite-de-France-Galop-2023-1.pdf</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>proprietaire_chevaux</t>
+        </is>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>galopeur</t>
+        </is>
+      </c>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="Q164" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>B-à qualifier (association)</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Philippe Germond</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Propriétaire, membre du Conseil d'Administration de France Galop</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>France Galop</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr"/>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Philippe%20Germond</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr"/>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Propriétaire de galopeurs, membre du CA (NB: homonyme possible du dirigeant télécoms/médias)</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>Présentation des nouvelles instances de France Galop</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>https://www.lecheval.fr/article/presentation-des-nouvelles-instances-de-france-galop/30208</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>proprietaire_chevaux</t>
+        </is>
+      </c>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>galopeur</t>
+        </is>
+      </c>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="Q165" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>B-à qualifier (association)</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Francis Teboul</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Propriétaire, membre du Conseil d'Administration de France Galop</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>France Galop</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Francis%20Teboul</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr"/>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Propriétaire de galopeurs, membre du CA</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>Présentation des nouvelles instances de France Galop</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>https://www.lecheval.fr/article/presentation-des-nouvelles-instances-de-france-galop/30208</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>proprietaire_chevaux</t>
+        </is>
+      </c>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>galopeur</t>
+        </is>
+      </c>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="Q166" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>B-à qualifier (association)</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Anthony Baudoin</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Éleveur, membre du CA de France Galop (profession à confirmer)</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>France Galop</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr"/>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Anthony%20Baudoin</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr"/>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Éleveur de galopeurs, membre du CA</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>Présentation des nouvelles instances de France Galop</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>https://www.lecheval.fr/article/presentation-des-nouvelles-instances-de-france-galop/30208</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>proprietaire_chevaux</t>
+        </is>
+      </c>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>galopeur</t>
+        </is>
+      </c>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="Q167" t="inlineStr">
+        <is>
+          <t>27.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>B-à qualifier (association)</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Nicolas de Chambure</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Éleveur (Haras d'Etreham), membre du CA de France Galop</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Haras d'Etreham</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr"/>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Nicolas%20de%20Chambure</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr"/>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Éleveur-dirigeant du Haras d'Etreham, membre du CA France Galop</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>Présentation des nouvelles instances de France Galop</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>https://www.lecheval.fr/article/presentation-des-nouvelles-instances-de-france-galop/30208</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>proprietaire_chevaux</t>
+        </is>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>haras</t>
+        </is>
+      </c>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="Q168" t="inlineStr">
+        <is>
+          <t>27.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>B-à qualifier (association)</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Jean-Luc A. Chartier</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Avocat; Président de la Fédération Française de Polo (depuis 2006)</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Cabinet d'avocat / FFP</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr"/>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Jean-Luc%20A.%20Chartier</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr"/>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Président de la FF Polo, joueur et dirigeant du polo français</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>Wikipédia FFP + statuts fédéraux</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>https://fr.wikipedia.org/wiki/F%C3%A9d%C3%A9ration_fran%C3%A7aise_de_polo</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>cavalier_pratiquant</t>
+        </is>
+      </c>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>polo</t>
+        </is>
+      </c>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="Q169" t="inlineStr">
+        <is>
+          <t>63.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>B-à qualifier (association)</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Xavier Doumen</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Secrétaire Général de la FF Polo (profession à confirmer)</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>FF Polo</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Xavier%20Doumen</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr"/>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Membre du comité fédéral et SG de la FF Polo</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>Statuts et règlements FFP</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>https://www.francepolo.com/statuts-et-reglements/</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>cavalier_pratiquant</t>
+        </is>
+      </c>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>polo</t>
+        </is>
+      </c>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="Q170" t="inlineStr">
+        <is>
+          <t>35.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>B-à qualifier (association)</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Éric Le Maire</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Membre du comité directeur FF Polo (profession à confirmer)</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>FF Polo</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Éric%20Le%20Maire</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr"/>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>Membre du comité fédéral de la FF Polo (joueur)</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>Statuts et règlements FFP</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>https://www.francepolo.com/statuts-et-reglements/</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>cavalier_pratiquant</t>
+        </is>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>polo</t>
+        </is>
+      </c>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="Q171" t="inlineStr">
+        <is>
+          <t>49.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>B-à qualifier (association)</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Bernard Perin</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Membre du comité directeur FF Polo (profession à confirmer)</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>FF Polo</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr"/>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Bernard%20Perin</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr"/>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>Membre du comité fédéral de la FF Polo (joueur)</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>Statuts et règlements FFP</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>https://www.francepolo.com/statuts-et-reglements/</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>cavalier_pratiquant</t>
+        </is>
+      </c>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>polo</t>
+        </is>
+      </c>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="Q172" t="inlineStr">
+        <is>
+          <t>49.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>B-à qualifier (association)</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Thierry Vétois</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Membre du comité directeur FF Polo (profession à confirmer)</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>FF Polo</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr"/>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Thierry%20Vétois</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr"/>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>Membre du comité fédéral de la FF Polo (joueur)</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>Statuts et règlements FFP</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>https://www.francepolo.com/statuts-et-reglements/</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>cavalier_pratiquant</t>
+        </is>
+      </c>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>polo</t>
+        </is>
+      </c>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="Q173" t="inlineStr">
+        <is>
+          <t>49.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>B-à qualifier (association)</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Naïma Rezkallah</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Médecin; membre du comité directeur FF Polo</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Cabinet médical / FFP</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr"/>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Naïma%20Rezkallah</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr"/>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>Médecin membre du comité fédéral de la FF Polo</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>Statuts et règlements FFP</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>https://www.francepolo.com/statuts-et-reglements/</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>cavalier_pratiquant</t>
+        </is>
+      </c>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>polo</t>
+        </is>
+      </c>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="Q174" t="inlineStr">
+        <is>
+          <t>49.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>B-à qualifier (association)</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Anna Salter</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Vétérinaire; membre du comité directeur FF Polo</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Cabinet vétérinaire / FFP</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr"/>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Anna%20Salter</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr"/>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>Vétérinaire membre du comité fédéral de la FF Polo</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>Statuts et règlements FFP</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>https://www.francepolo.com/statuts-et-reglements/</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>cavalier_pratiquant</t>
+        </is>
+      </c>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>polo</t>
+        </is>
+      </c>
+      <c r="P175" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="Q175" t="inlineStr">
+        <is>
+          <t>49.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>B-à qualifier (association)</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Philippe Bosque</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Trésorier UNAT Sud-Ouest (profession à confirmer)</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>UNAT Sud-Ouest</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr"/>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Philippe%20Bosque</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr"/>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>Amateur de trot, trésorier régional UNAT</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>Administration UNAT Sud-Ouest</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>https://unat.fr/administration/</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>aucun</t>
+        </is>
+      </c>
+      <c r="O176" t="inlineStr"/>
+      <c r="P176" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q176" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>B-à qualifier (association)</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Thomas Bosque</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Trésorier adjoint UNAT Sud-Ouest (profession à confirmer)</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>UNAT Sud-Ouest</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr"/>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Thomas%20Bosque</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr"/>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>Amateur de trot, bureau régional UNAT</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>Administration UNAT Sud-Ouest</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>https://unat.fr/administration/</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>aucun</t>
+        </is>
+      </c>
+      <c r="O177" t="inlineStr"/>
+      <c r="P177" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q177" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>B-à qualifier (association)</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Alain Rivière</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Secrétaire Général UNAT Sud-Ouest (profession à confirmer)</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>UNAT Sud-Ouest</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr"/>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Alain%20Rivière</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr"/>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>Amateur de trot, bureau régional UNAT</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>Administration UNAT Sud-Ouest</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>https://unat.fr/administration/</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>aucun</t>
+        </is>
+      </c>
+      <c r="O178" t="inlineStr"/>
+      <c r="P178" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q178" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>B-à qualifier (association)</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Léa Lizée</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Secrétaire adjointe UNAT Sud-Ouest (profession à confirmer)</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>UNAT Sud-Ouest</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr"/>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Léa%20Lizée</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr"/>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>Amatrice de trot, bureau régional UNAT</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>Administration UNAT Sud-Ouest</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>https://unat.fr/administration/</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>aucun</t>
+        </is>
+      </c>
+      <c r="O179" t="inlineStr"/>
+      <c r="P179" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q179" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>B-à qualifier (association)</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Stéphane Dersoir</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Trésorier UNAT Normandie (profession à confirmer)</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>UNAT Normandie</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr"/>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Stéphane%20Dersoir</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr"/>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>Amateur de trot, bureau régional UNAT</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>Administration UNAT Normandie</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>https://unat.fr/normandie-administration/</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>aucun</t>
+        </is>
+      </c>
+      <c r="O180" t="inlineStr"/>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q180" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>B-à qualifier (association)</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Lara Lefebvre</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Secrétaire Générale UNAT Normandie (profession à confirmer)</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>UNAT Normandie</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr"/>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Lara%20Lefebvre</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr"/>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>Amatrice de trot, bureau régional UNAT</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>Administration UNAT Normandie</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>https://unat.fr/normandie-administration/</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>aucun</t>
+        </is>
+      </c>
+      <c r="O181" t="inlineStr"/>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q181" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>B-à qualifier (association)</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Sophie Blanchetière</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Trésorière-secrétaire UNAT Sud-Est; driver amateur reconnue</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>UNAT Sud-Est</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr"/>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Sophie%20Blanchetière</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr"/>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>Driver amateur célèbre du trot, dirigeante associative UNAT</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>Administration UNAT Sud-Est + presse trot</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>https://unat.fr/unat-sud-est-administration/</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>aucun</t>
+        </is>
+      </c>
+      <c r="O182" t="inlineStr"/>
+      <c r="P182" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q182" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>A-presse</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Serge Demeautis</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Chef d'entreprise; président de la Société des Courses de Carentan (depuis 2019)</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Société des Courses de Carentan</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Carentan (50)</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Serge%20Demeautis</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr"/>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>Chef d'entreprise ET président d'hippodrome (double signal prouvé)</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>Hommage FNCH : chef d'entreprise, président des courses de Carentan</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>https://www.fnch.fr/national/actualit%C3%A9s/hommage-trois-presidents-de-societes-de-courses-recemment-disparus</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>aucun</t>
+        </is>
+      </c>
+      <c r="O183" t="inlineStr"/>
+      <c r="P183" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q183" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>B-à qualifier (presse)</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Jean-Jacques Saunon</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Président de la Société des Courses de Montluçon depuis 1998 (profession à confirmer)</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Société des Courses de Montluçon</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Montluçon (03)</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Jean-Jacques%20Saunon</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr"/>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>Président bénévole d'hippodrome depuis 25+ ans</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>Site officiel de l'hippodrome de Montluçon</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>https://www.hippodrome-montlucon.com/la-societe-des-courses/</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>aucun</t>
+        </is>
+      </c>
+      <c r="O184" t="inlineStr"/>
+      <c r="P184" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q184" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>B-à qualifier (association)</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Antonia Devin</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Membre du CA de France Galop; commission santé Fédération des Éleveurs (profession à confirmer)</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>France Galop</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr"/>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Antonia%20Devin</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr"/>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>Propriétaire-éleveuse de galopeurs, administratrice</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>Représentants FPG dans les instances</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>https://www.fede-proprietairesdugalop.fr/vos-repr%C3%A9sentants-dans-institution</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>proprietaire_chevaux</t>
+        </is>
+      </c>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>galopeur</t>
+        </is>
+      </c>
+      <c r="P185" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="Q185" t="inlineStr">
+        <is>
+          <t>27.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>B-à qualifier (association)</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Loïc Malivet</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Vice-président de France Galop; président de la Fédération des Éleveurs du Galop</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>France Galop / Fédération des Éleveurs</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr"/>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Loïc%20Malivet</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr"/>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>Éleveur-propriétaire, VP France Galop</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>Représentants FPG dans les instances</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>https://www.fede-proprietairesdugalop.fr/vos-repr%C3%A9sentants-dans-institution</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>proprietaire_chevaux</t>
+        </is>
+      </c>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>france galop</t>
+        </is>
+      </c>
+      <c r="P186" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="Q186" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>B-à qualifier (association)</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Antoine Gilibert</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Propriétaire depuis 1987; président de la Société des Courses de Compiègne (profession à confirmer)</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Société des Courses de Compiègne</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Compiègne (60)</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Antoine%20Gilibert</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr"/>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>Propriétaire de galopeurs + président d'hippodrome</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>Représentants FPG dans les instances</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>https://www.fede-proprietairesdugalop.fr/vos-repr%C3%A9sentants-dans-institution</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>proprietaire_chevaux</t>
+        </is>
+      </c>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>galopeur</t>
+        </is>
+      </c>
+      <c r="P187" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="Q187" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>B-à qualifier (association)</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Serge Tardy</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Président de l'APGO « Les Propriétaires au Galop » (profession à confirmer)</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>APGO</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr"/>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Serge%20Tardy</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr"/>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>Propriétaire de galopeurs, président d'association de propriétaires</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>Réélu président de l'APGO (site officiel)</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>https://www.apgo-galop.fr/Actualites.H/b46513a/LES-PROPRIETAIRES-AU-GALOP-SERGE-TARDY-REELU-PRESIDENT-</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>proprietaire_chevaux</t>
+        </is>
+      </c>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>galopeur</t>
+        </is>
+      </c>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="Q188" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>B-à qualifier (association)</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Docteur Colombu</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Médecin; ex-vice-président de France Galop</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Cabinet médical / France Galop</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr"/>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Docteur%20Colombu</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr"/>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>Médecin ET dirigeant historique des courses au galop</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>Représentants FPG dans les instances</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>https://www.fede-proprietairesdugalop.fr/vos-repr%C3%A9sentants-dans-institution</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>proprietaire_chevaux</t>
+        </is>
+      </c>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>france galop</t>
+        </is>
+      </c>
+      <c r="P189" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="Q189" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>B-à qualifier (association)</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Nancy Marandon</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Présidente du Syndicat National des Propriétaires de Trotteurs (profession à confirmer)</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>SNPT</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Nancy%20Marandon</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr"/>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>Propriétaire de trotteurs, présidente du syndicat national</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>Organigramme SNPT + Le Trot</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>https://snpt.net/index.php?Itemid=143&amp;id=91&amp;layout=item&amp;option=com_k2&amp;view=item</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>proprietaire_chevaux</t>
+        </is>
+      </c>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>trotteur</t>
+        </is>
+      </c>
+      <c r="P190" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="Q190" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>B-à qualifier (association)</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Jean-François Bassard</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Vice-président du SNPT (profession à confirmer)</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>SNPT</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr"/>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Jean-François%20Bassard</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr"/>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>Propriétaire de trotteurs, VP du syndicat</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>Organigramme SNPT</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>https://snpt.net/index.php?Itemid=143&amp;id=91&amp;layout=item&amp;option=com_k2&amp;view=item</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>proprietaire_chevaux</t>
+        </is>
+      </c>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>trotteur</t>
+        </is>
+      </c>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="Q191" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>B-à qualifier (association)</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Philippe Levasseur</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Vice-président du SNPT (profession à confirmer)</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>SNPT</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr"/>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Philippe%20Levasseur</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr"/>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>Propriétaire de trotteurs, VP du syndicat</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>Organigramme SNPT</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>https://snpt.net/index.php?Itemid=143&amp;id=91&amp;layout=item&amp;option=com_k2&amp;view=item</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>proprietaire_chevaux</t>
+        </is>
+      </c>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>trotteur</t>
+        </is>
+      </c>
+      <c r="P192" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="Q192" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>B-à qualifier (association)</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Éric Godard</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Vice-président du SNPT (profession à confirmer)</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>SNPT</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr"/>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Éric%20Godard</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr"/>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>Propriétaire de trotteurs, VP du syndicat</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>Organigramme SNPT</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>https://snpt.net/index.php?Itemid=143&amp;id=91&amp;layout=item&amp;option=com_k2&amp;view=item</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t>proprietaire_chevaux</t>
+        </is>
+      </c>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>trotteur</t>
+        </is>
+      </c>
+      <c r="P193" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="Q193" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>B-à qualifier (association)</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Éric Bussy</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Trésorier du SNPT (profession à confirmer)</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>SNPT</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr"/>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Éric%20Bussy</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr"/>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>Propriétaire de trotteurs, trésorier du syndicat</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>Organigramme SNPT</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>https://snpt.net/index.php?Itemid=143&amp;id=91&amp;layout=item&amp;option=com_k2&amp;view=item</t>
+        </is>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>proprietaire_chevaux</t>
+        </is>
+      </c>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>trotteur</t>
+        </is>
+      </c>
+      <c r="P194" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="Q194" t="inlineStr">
+        <is>
+          <t>27.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>B-à qualifier (association)</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Pierre-Jean Alaux</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Représentant SNPT à la commission du code des courses (profession à confirmer)</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>SNPT</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr"/>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Pierre-Jean%20Alaux</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr"/>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>Propriétaire de trotteurs, représentant syndical</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>Organigramme SNPT</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>https://snpt.net/index.php?Itemid=143&amp;id=91&amp;layout=item&amp;option=com_k2&amp;view=item</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>proprietaire_chevaux</t>
+        </is>
+      </c>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>trotteur</t>
+        </is>
+      </c>
+      <c r="P195" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="Q195" t="inlineStr">
+        <is>
+          <t>27.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>B-à qualifier (association)</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Jean-Louis Colombier</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Représentant SNPT à la commission des programmes (profession à confirmer)</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>SNPT</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr"/>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Jean-Louis%20Colombier</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr"/>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>Propriétaire de trotteurs, représentant syndical</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>Organigramme SNPT</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>https://snpt.net/index.php?Itemid=143&amp;id=91&amp;layout=item&amp;option=com_k2&amp;view=item</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N196" t="inlineStr">
+        <is>
+          <t>proprietaire_chevaux</t>
+        </is>
+      </c>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>trotteur</t>
+        </is>
+      </c>
+      <c r="P196" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="Q196" t="inlineStr">
+        <is>
+          <t>27.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>B-à qualifier (association)</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>James Carpentier</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Représentant SNPT au livre généalogique du Trotteur Français (profession à confirmer)</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>SNPT</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr"/>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=James%20Carpentier</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr"/>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>Propriétaire de trotteurs, représentant syndical</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>Organigramme SNPT</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>https://snpt.net/index.php?Itemid=143&amp;id=91&amp;layout=item&amp;option=com_k2&amp;view=item</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>proprietaire_chevaux</t>
+        </is>
+      </c>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>trotteur</t>
+        </is>
+      </c>
+      <c r="P197" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="Q197" t="inlineStr">
+        <is>
+          <t>27.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>B-à qualifier (association)</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Caroline Sionneau</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Propriétaire élue au Comité SETF/Le Trot 2023 - collège propriétaires (profession à confirmer)</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>SETF / Le Trot</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr"/>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Caroline%20Sionneau</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr"/>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>Propriétaire de trotteurs, élue nationale (1002 voix)</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>Résultats complets élections Le Trot 2023 (Equidia)</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>https://www.equidia.fr/articles/actualite/elections-le-trot-les-quatre-candidats-a-la-presidence-elus</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>proprietaire_chevaux</t>
+        </is>
+      </c>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>trotteur</t>
+        </is>
+      </c>
+      <c r="P198" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="Q198" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>B-à qualifier (association)</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Gilles Jeziorski</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Propriétaire élu au Comité SETF/Le Trot 2023 (profession à confirmer)</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>SETF / Le Trot</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr"/>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Gilles%20Jeziorski</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr"/>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>Propriétaire de trotteurs, élu national (817 voix)</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>Résultats complets élections Le Trot 2023 (Equidia)</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>https://www.equidia.fr/articles/actualite/elections-le-trot-les-quatre-candidats-a-la-presidence-elus</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>proprietaire_chevaux</t>
+        </is>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>trotteur</t>
+        </is>
+      </c>
+      <c r="P199" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="Q199" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>B-à qualifier (association)</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Pierre-Joseph Goetz</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Propriétaire élu au Comité SETF/Le Trot 2023 (profession à confirmer)</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>SETF / Le Trot</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr"/>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Pierre-Joseph%20Goetz</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr"/>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>Propriétaire de trotteurs, élu national (739 voix)</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>Résultats complets élections Le Trot 2023 (Equidia)</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>https://www.equidia.fr/articles/actualite/elections-le-trot-les-quatre-candidats-a-la-presidence-elus</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>proprietaire_chevaux</t>
+        </is>
+      </c>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>trotteur</t>
+        </is>
+      </c>
+      <c r="P200" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="Q200" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>B-à qualifier (association)</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Alain Sinenberg</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Propriétaire élu(e) régional(e) SETF/Le Trot 2023 - collège propriétaires (profession à confirmer)</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>SETF / Le Trot</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr"/>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Alain%20Sinenberg</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr"/>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>Propriétaire de trotteurs, élu(e) aux instances régionales du Trot</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>Résultats officiels des élections SETF 2023 (letrot.com)</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>https://www.letrot.com/actualites/elections-tous-les-resultats-17758</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>proprietaire_chevaux</t>
+        </is>
+      </c>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>trotteur</t>
+        </is>
+      </c>
+      <c r="P201" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="Q201" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>B-à qualifier (association)</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Gilles Raffre</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Propriétaire élu(e) régional(e) SETF/Le Trot 2023 - collège propriétaires (profession à confirmer)</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>SETF / Le Trot</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr"/>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Gilles%20Raffre</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr"/>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>Propriétaire de trotteurs, élu(e) aux instances régionales du Trot</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>Résultats officiels des élections SETF 2023 (letrot.com)</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>https://www.letrot.com/actualites/elections-tous-les-resultats-17758</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>proprietaire_chevaux</t>
+        </is>
+      </c>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>trotteur</t>
+        </is>
+      </c>
+      <c r="P202" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="Q202" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>B-à qualifier (association)</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Pierre-Yves Airiaud</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Propriétaire élu(e) régional(e) SETF/Le Trot 2023 - collège propriétaires (profession à confirmer)</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>SETF / Le Trot</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr"/>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Pierre-Yves%20Airiaud</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr"/>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>Propriétaire de trotteurs, élu(e) aux instances régionales du Trot</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>Résultats officiels des élections SETF 2023 (letrot.com)</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>https://www.letrot.com/actualites/elections-tous-les-resultats-17758</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>proprietaire_chevaux</t>
+        </is>
+      </c>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>trotteur</t>
+        </is>
+      </c>
+      <c r="P203" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="Q203" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>B-à qualifier (association)</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Ivan Jublot</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Propriétaire élu(e) régional(e) SETF/Le Trot 2023 - collège propriétaires (profession à confirmer)</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>SETF / Le Trot</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr"/>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Ivan%20Jublot</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr"/>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>Propriétaire de trotteurs, élu(e) aux instances régionales du Trot</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>Résultats officiels des élections SETF 2023 (letrot.com)</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>https://www.letrot.com/actualites/elections-tous-les-resultats-17758</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>proprietaire_chevaux</t>
+        </is>
+      </c>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>trotteur</t>
+        </is>
+      </c>
+      <c r="P204" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="Q204" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>B-à qualifier (association)</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Élisabeth Allaire</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Propriétaire élu(e) régional(e) SETF/Le Trot 2023 - collège propriétaires (profession à confirmer)</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>SETF / Le Trot</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr"/>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Élisabeth%20Allaire</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr"/>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>Propriétaire de trotteurs, élu(e) aux instances régionales du Trot</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>Résultats officiels des élections SETF 2023 (letrot.com)</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>https://www.letrot.com/actualites/elections-tous-les-resultats-17758</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>proprietaire_chevaux</t>
+        </is>
+      </c>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>trotteur</t>
+        </is>
+      </c>
+      <c r="P205" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="Q205" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>B-à qualifier (association)</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Daniel Grimault</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Propriétaire élu(e) régional(e) SETF/Le Trot 2023 - collège propriétaires (profession à confirmer)</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>SETF / Le Trot</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr"/>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Daniel%20Grimault</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr"/>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>Propriétaire de trotteurs, élu(e) aux instances régionales du Trot</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>Résultats officiels des élections SETF 2023 (letrot.com)</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>https://www.letrot.com/actualites/elections-tous-les-resultats-17758</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>proprietaire_chevaux</t>
+        </is>
+      </c>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>trotteur</t>
+        </is>
+      </c>
+      <c r="P206" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="Q206" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>B-à qualifier (association)</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Sébastien Moureaux</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Propriétaire élu(e) régional(e) SETF/Le Trot 2023 - collège propriétaires (profession à confirmer)</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>SETF / Le Trot</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr"/>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Sébastien%20Moureaux</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr"/>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>Propriétaire de trotteurs, élu(e) aux instances régionales du Trot</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>Résultats officiels des élections SETF 2023 (letrot.com)</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>https://www.letrot.com/actualites/elections-tous-les-resultats-17758</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>proprietaire_chevaux</t>
+        </is>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>trotteur</t>
+        </is>
+      </c>
+      <c r="P207" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="Q207" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>B-à qualifier (association)</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Lynda Pacha</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Propriétaire élu(e) régional(e) SETF/Le Trot 2023 - collège propriétaires (profession à confirmer)</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>SETF / Le Trot</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr"/>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Lynda%20Pacha</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr"/>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>Propriétaire de trotteurs, élu(e) aux instances régionales du Trot</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>Résultats officiels des élections SETF 2023 (letrot.com)</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>https://www.letrot.com/actualites/elections-tous-les-resultats-17758</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>proprietaire_chevaux</t>
+        </is>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>trotteur</t>
+        </is>
+      </c>
+      <c r="P208" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="Q208" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>B-à qualifier (association)</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Valérie Abrivard</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Propriétaire élu(e) régional(e) SETF/Le Trot 2023 - collège propriétaires (profession à confirmer)</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>SETF / Le Trot</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr"/>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Valérie%20Abrivard</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr"/>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>Propriétaire de trotteurs, élu(e) aux instances régionales du Trot</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>Résultats officiels des élections SETF 2023 (letrot.com)</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>https://www.letrot.com/actualites/elections-tous-les-resultats-17758</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>proprietaire_chevaux</t>
+        </is>
+      </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>trotteur</t>
+        </is>
+      </c>
+      <c r="P209" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="Q209" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>B-à qualifier (association)</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Rachel Popot</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Propriétaire élu(e) régional(e) SETF/Le Trot 2023 - collège propriétaires (profession à confirmer)</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>SETF / Le Trot</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr"/>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Rachel%20Popot</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr"/>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>Propriétaire de trotteurs, élu(e) aux instances régionales du Trot</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>Résultats officiels des élections SETF 2023 (letrot.com)</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>https://www.letrot.com/actualites/elections-tous-les-resultats-17758</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>proprietaire_chevaux</t>
+        </is>
+      </c>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>trotteur</t>
+        </is>
+      </c>
+      <c r="P210" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="Q210" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>B-à qualifier (association)</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Christian Le Barbey</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Propriétaire élu(e) régional(e) SETF/Le Trot 2023 - collège propriétaires (profession à confirmer)</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>SETF / Le Trot</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr"/>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Christian%20Le%20Barbey</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr"/>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>Propriétaire de trotteurs, élu(e) aux instances régionales du Trot</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>Résultats officiels des élections SETF 2023 (letrot.com)</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>https://www.letrot.com/actualites/elections-tous-les-resultats-17758</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>proprietaire_chevaux</t>
+        </is>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>trotteur</t>
+        </is>
+      </c>
+      <c r="P211" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="Q211" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>B-à qualifier (association)</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Tanguy de La Bourdonnaye</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Propriétaire élu(e) régional(e) SETF/Le Trot 2023 - collège propriétaires (profession à confirmer)</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>SETF / Le Trot</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr"/>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Tanguy%20de%20La%20Bourdonnaye</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr"/>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>Propriétaire de trotteurs, élu(e) aux instances régionales du Trot</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>Résultats officiels des élections SETF 2023 (letrot.com)</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>https://www.letrot.com/actualites/elections-tous-les-resultats-17758</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>proprietaire_chevaux</t>
+        </is>
+      </c>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>trotteur</t>
+        </is>
+      </c>
+      <c r="P212" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="Q212" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>B-à qualifier (association)</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Léa Barbe</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Propriétaire élu(e) régional(e) SETF/Le Trot 2023 - collège propriétaires (profession à confirmer)</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>SETF / Le Trot</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr"/>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Léa%20Barbe</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr"/>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>Propriétaire de trotteurs, élu(e) aux instances régionales du Trot</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>Résultats officiels des élections SETF 2023 (letrot.com)</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>https://www.letrot.com/actualites/elections-tous-les-resultats-17758</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>proprietaire_chevaux</t>
+        </is>
+      </c>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>trotteur</t>
+        </is>
+      </c>
+      <c r="P213" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="Q213" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>B-à qualifier (association)</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Pascal Bernard</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Propriétaire élu(e) régional(e) SETF/Le Trot 2023 - collège propriétaires (profession à confirmer)</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>SETF / Le Trot</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr"/>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Pascal%20Bernard</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr"/>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>Propriétaire de trotteurs, élu(e) aux instances régionales du Trot</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>Résultats officiels des élections SETF 2023 (letrot.com)</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>https://www.letrot.com/actualites/elections-tous-les-resultats-17758</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>proprietaire_chevaux</t>
+        </is>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>trotteur</t>
+        </is>
+      </c>
+      <c r="P214" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="Q214" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>B-à qualifier (association)</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Hughes Levesque</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Propriétaire élu(e) régional(e) SETF/Le Trot 2023 - collège propriétaires (profession à confirmer)</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>SETF / Le Trot</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr"/>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Hughes%20Levesque</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr"/>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>Propriétaire de trotteurs, élu(e) aux instances régionales du Trot</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>Résultats officiels des élections SETF 2023 (letrot.com)</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>https://www.letrot.com/actualites/elections-tous-les-resultats-17758</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>proprietaire_chevaux</t>
+        </is>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>trotteur</t>
+        </is>
+      </c>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="Q215" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>B-à qualifier (association)</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Patrice Dessartre</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Propriétaire élu(e) régional(e) SETF/Le Trot 2023 - collège propriétaires (profession à confirmer)</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>SETF / Le Trot</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr"/>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Patrice%20Dessartre</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr"/>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>Propriétaire de trotteurs, élu(e) aux instances régionales du Trot</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>Résultats officiels des élections SETF 2023 (letrot.com)</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>https://www.letrot.com/actualites/elections-tous-les-resultats-17758</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>proprietaire_chevaux</t>
+        </is>
+      </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>trotteur</t>
+        </is>
+      </c>
+      <c r="P216" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="Q216" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>B-à qualifier (association)</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Christelle Jacqueline David</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Propriétaire élu(e) régional(e) SETF/Le Trot 2023 - collège propriétaires (profession à confirmer)</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>SETF / Le Trot</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr"/>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Christelle%20Jacqueline%20David</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr"/>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>Propriétaire de trotteurs, élu(e) aux instances régionales du Trot</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>Résultats officiels des élections SETF 2023 (letrot.com)</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>https://www.letrot.com/actualites/elections-tous-les-resultats-17758</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>proprietaire_chevaux</t>
+        </is>
+      </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>trotteur</t>
+        </is>
+      </c>
+      <c r="P217" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="Q217" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>B-à qualifier (association)</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Gwenaëlle Ollier</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Propriétaire élu(e) régional(e) SETF/Le Trot 2023 - collège propriétaires (profession à confirmer)</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>SETF / Le Trot</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr"/>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Gwenaëlle%20Ollier</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr"/>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>Propriétaire de trotteurs, élu(e) aux instances régionales du Trot</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>Résultats officiels des élections SETF 2023 (letrot.com)</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>https://www.letrot.com/actualites/elections-tous-les-resultats-17758</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>proprietaire_chevaux</t>
+        </is>
+      </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>trotteur</t>
+        </is>
+      </c>
+      <c r="P218" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="Q218" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>B-à qualifier (association)</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Vincent Viel</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Propriétaire élu(e) régional(e) SETF/Le Trot 2023 - collège propriétaires (profession à confirmer)</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>SETF / Le Trot</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr"/>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Vincent%20Viel</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr"/>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>Propriétaire de trotteurs, élu(e) aux instances régionales du Trot</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>Résultats officiels des élections SETF 2023 (letrot.com)</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>https://www.letrot.com/actualites/elections-tous-les-resultats-17758</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>proprietaire_chevaux</t>
+        </is>
+      </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>trotteur</t>
+        </is>
+      </c>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="Q219" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>B-à qualifier (association)</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Axelle Nègre de Watrigant</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Présidente du Comité Régional du galop Sud-Ouest (profession à confirmer)</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>France Galop (région Sud-Ouest)</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr"/>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Axelle%20Nègre%20de%20Watrigant</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr"/>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>Dirigeante élue des courses au galop du Sud-Ouest</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>Élections France Galop 2023 (Jour de Galop)</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>https://www.jourdegalop.com/2023/10/elections-2023-une-journee-particuliere</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>proprietaire_chevaux</t>
+        </is>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>france galop</t>
+        </is>
+      </c>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="Q220" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>B-à qualifier (association)</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Philippe Faucampré</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Président des Propriétaires au Galop Sud-Est et Corse (profession à confirmer)</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Syndicat des propriétaires (galop)</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr"/>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Philippe%20Faucampré</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr"/>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>Propriétaire de galopeurs, président régional du syndicat</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>Processus électoral du syndicat (France Sire)</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>https://www.france-sire.com/article-actualites-42533-lancement_du_processus_electoral_pour_la_presidence_du_syndicat_national_des_proprietaires.php</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>proprietaire_chevaux</t>
+        </is>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>galopeur</t>
+        </is>
+      </c>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="Q221" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/prospects.xlsx
+++ b/data/prospects.xlsx
@@ -422,26 +422,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q221"/>
+  <dimension ref="A1:S229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="38" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="45" customWidth="1" min="9" max="9"/>
-    <col width="55" customWidth="1" min="10" max="10"/>
-    <col width="45" customWidth="1" min="11" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
     <col width="22" customWidth="1" min="15" max="15"/>
-    <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
+    <col width="22" customWidth="1" min="18" max="18"/>
+    <col width="22" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -530,6 +532,16 @@
           <t>score</t>
         </is>
       </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>taille_estimee</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cible_accessible</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -613,6 +625,16 @@
           <t>72.7</t>
         </is>
       </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>grande fortune / célébrité</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -696,6 +718,16 @@
           <t>72.7</t>
         </is>
       </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>grande fortune / célébrité</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -775,6 +807,16 @@
           <t>49.0</t>
         </is>
       </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -854,6 +896,16 @@
           <t>49.0</t>
         </is>
       </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>grande entreprise (&gt;100)</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -937,6 +989,16 @@
           <t>88.2</t>
         </is>
       </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>grande fortune / célébrité</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1020,6 +1082,16 @@
           <t>72.0</t>
         </is>
       </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>grande fortune / célébrité</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1103,6 +1175,16 @@
           <t>85.5</t>
         </is>
       </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>grande fortune / célébrité</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1182,6 +1264,16 @@
           <t>68.8</t>
         </is>
       </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>grande fortune / célébrité</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1265,6 +1357,16 @@
           <t>68.8</t>
         </is>
       </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>grande fortune / célébrité</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1348,6 +1450,16 @@
           <t>53.5</t>
         </is>
       </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>grande fortune / célébrité</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1431,6 +1543,16 @@
           <t>72.7</t>
         </is>
       </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>grande fortune / célébrité</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1514,6 +1636,16 @@
           <t>72.7</t>
         </is>
       </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>grande fortune / célébrité</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1597,6 +1729,16 @@
           <t>72.7</t>
         </is>
       </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>grande fortune / célébrité</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1680,6 +1822,16 @@
           <t>61.2</t>
         </is>
       </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>grande fortune / célébrité</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1763,6 +1915,16 @@
           <t>52.5</t>
         </is>
       </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>grande entreprise (&gt;100)</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1846,6 +2008,16 @@
           <t>81.0</t>
         </is>
       </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>grande fortune / célébrité</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1929,6 +2101,16 @@
           <t>81.0</t>
         </is>
       </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>grande fortune / célébrité</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2012,6 +2194,16 @@
           <t>88.2</t>
         </is>
       </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>grande fortune / célébrité</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2095,6 +2287,16 @@
           <t>85.5</t>
         </is>
       </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>grande fortune / célébrité</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2178,6 +2380,16 @@
           <t>38.0</t>
         </is>
       </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>grande fortune / célébrité</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2261,6 +2473,16 @@
           <t>81.0</t>
         </is>
       </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>grande fortune / célébrité</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2344,6 +2566,16 @@
           <t>65.0</t>
         </is>
       </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>grande fortune / célébrité</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2427,6 +2659,16 @@
           <t>65.0</t>
         </is>
       </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>grande fortune / célébrité</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2506,6 +2748,16 @@
           <t>72.7</t>
         </is>
       </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>grande fortune / célébrité</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2589,6 +2841,16 @@
           <t>42.5</t>
         </is>
       </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>grande fortune / célébrité</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2672,6 +2934,16 @@
           <t>72.0</t>
         </is>
       </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>grande fortune / célébrité</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2755,6 +3027,16 @@
           <t>72.7</t>
         </is>
       </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>grande fortune / célébrité</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2838,6 +3120,16 @@
           <t>72.7</t>
         </is>
       </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>grande fortune / célébrité</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2921,6 +3213,16 @@
           <t>68.8</t>
         </is>
       </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>grande fortune / célébrité</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3004,6 +3306,16 @@
           <t>65.0</t>
         </is>
       </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3087,6 +3399,16 @@
           <t>68.0</t>
         </is>
       </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>grande entreprise (&gt;100)</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3170,6 +3492,16 @@
           <t>61.2</t>
         </is>
       </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>grande entreprise (&gt;100)</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3253,6 +3585,16 @@
           <t>36.7</t>
         </is>
       </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>grande entreprise (&gt;100)</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3336,6 +3678,16 @@
           <t>47.2</t>
         </is>
       </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>grande entreprise (&gt;100)</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3419,6 +3771,16 @@
           <t>47.2</t>
         </is>
       </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>grande entreprise (&gt;100)</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3502,6 +3864,16 @@
           <t>47.2</t>
         </is>
       </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>grande entreprise (&gt;100)</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3585,6 +3957,16 @@
           <t>47.2</t>
         </is>
       </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>grande entreprise (&gt;100)</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3668,6 +4050,16 @@
           <t>36.7</t>
         </is>
       </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>grande entreprise (&gt;100)</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3747,6 +4139,16 @@
           <t>36.7</t>
         </is>
       </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>grande entreprise (&gt;100)</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3830,6 +4232,16 @@
           <t>50.4</t>
         </is>
       </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>grande fortune / célébrité</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3913,6 +4325,16 @@
           <t>50.4</t>
         </is>
       </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>grande entreprise (&gt;100)</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3996,6 +4418,16 @@
           <t>47.2</t>
         </is>
       </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4075,6 +4507,16 @@
           <t>44.1</t>
         </is>
       </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>grande entreprise (&gt;100)</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4154,6 +4596,16 @@
           <t>29.4</t>
         </is>
       </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>grande entreprise (&gt;100)</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4237,6 +4689,16 @@
           <t>68.8</t>
         </is>
       </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>grande fortune / célébrité</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4318,6 +4780,16 @@
       <c r="Q47" t="inlineStr">
         <is>
           <t>50.4</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>oui</t>
         </is>
       </c>
     </row>
@@ -4395,6 +4867,16 @@
           <t>70.0</t>
         </is>
       </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4474,6 +4956,16 @@
           <t>31.8</t>
         </is>
       </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -4553,6 +5045,16 @@
           <t>63.0</t>
         </is>
       </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -4632,6 +5134,16 @@
           <t>16.8</t>
         </is>
       </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>grande entreprise (&gt;100)</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -4715,6 +5227,16 @@
           <t>14.7</t>
         </is>
       </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -4794,6 +5316,16 @@
           <t>12.2</t>
         </is>
       </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>grande entreprise (&gt;100)</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -4873,6 +5405,16 @@
           <t>12.2</t>
         </is>
       </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>grande entreprise (&gt;100)</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -4956,6 +5498,16 @@
           <t>42.0</t>
         </is>
       </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -5039,6 +5591,16 @@
           <t>42.0</t>
         </is>
       </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -5118,6 +5680,16 @@
           <t>63.0</t>
         </is>
       </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -5195,6 +5767,16 @@
       <c r="Q58" t="inlineStr">
         <is>
           <t>42.0</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>oui</t>
         </is>
       </c>
     </row>
@@ -5272,6 +5854,16 @@
           <t>70.0</t>
         </is>
       </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -5349,6 +5941,16 @@
       <c r="Q60" t="inlineStr">
         <is>
           <t>31.5</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>oui</t>
         </is>
       </c>
     </row>
@@ -5426,6 +6028,16 @@
           <t>28.0</t>
         </is>
       </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -5501,6 +6113,16 @@
           <t>28.0</t>
         </is>
       </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -5576,6 +6198,16 @@
           <t>28.0</t>
         </is>
       </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -5653,6 +6285,16 @@
       <c r="Q64" t="inlineStr">
         <is>
           <t>28.0</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>oui</t>
         </is>
       </c>
     </row>
@@ -5730,6 +6372,16 @@
           <t>28.0</t>
         </is>
       </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -5805,6 +6457,16 @@
           <t>28.0</t>
         </is>
       </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -5880,6 +6542,16 @@
           <t>28.0</t>
         </is>
       </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -5959,6 +6631,16 @@
           <t>0.0</t>
         </is>
       </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>grande entreprise (&gt;100)</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -6032,6 +6714,16 @@
       <c r="Q69" t="inlineStr">
         <is>
           <t>0.0</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>oui</t>
         </is>
       </c>
     </row>
@@ -6105,6 +6797,16 @@
           <t>0.0</t>
         </is>
       </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -6176,6 +6878,16 @@
           <t>0.0</t>
         </is>
       </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -6251,6 +6963,16 @@
           <t>0.0</t>
         </is>
       </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -6330,6 +7052,16 @@
           <t>0.0</t>
         </is>
       </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -6405,6 +7137,16 @@
           <t>0.0</t>
         </is>
       </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -6482,6 +7224,16 @@
       <c r="Q75" t="inlineStr">
         <is>
           <t>31.5</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>oui</t>
         </is>
       </c>
     </row>
@@ -6555,6 +7307,16 @@
           <t>0.0</t>
         </is>
       </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -6634,6 +7396,16 @@
           <t>28.4</t>
         </is>
       </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -6717,6 +7489,16 @@
           <t>42.0</t>
         </is>
       </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>grande entreprise (&gt;100)</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -6796,6 +7578,16 @@
           <t>63.0</t>
         </is>
       </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -6875,6 +7667,16 @@
           <t>0.0</t>
         </is>
       </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -6954,6 +7756,16 @@
           <t>0.0</t>
         </is>
       </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -7033,6 +7845,16 @@
           <t>0.0</t>
         </is>
       </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>grande entreprise (&gt;100)</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -7116,6 +7938,16 @@
           <t>42.0</t>
         </is>
       </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>grande entreprise (&gt;100)</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -7193,6 +8025,16 @@
       <c r="Q84" t="inlineStr">
         <is>
           <t>42.0</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>oui</t>
         </is>
       </c>
     </row>
@@ -7270,6 +8112,16 @@
           <t>28.0</t>
         </is>
       </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -7347,6 +8199,16 @@
       <c r="Q86" t="inlineStr">
         <is>
           <t>14.7</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>grande entreprise (&gt;100)</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>non</t>
         </is>
       </c>
     </row>
@@ -7420,6 +8282,16 @@
           <t>0.0</t>
         </is>
       </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -7499,6 +8371,16 @@
           <t>34.7</t>
         </is>
       </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -7578,6 +8460,16 @@
           <t>63.0</t>
         </is>
       </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -7661,6 +8553,16 @@
           <t>25.2</t>
         </is>
       </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -7744,6 +8646,16 @@
           <t>22.0</t>
         </is>
       </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -7827,6 +8739,16 @@
           <t>31.5</t>
         </is>
       </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>grande entreprise (&gt;100)</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -7910,6 +8832,16 @@
           <t>28.0</t>
         </is>
       </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>grande fortune / célébrité</t>
+        </is>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -7987,6 +8919,16 @@
       <c r="Q94" t="inlineStr">
         <is>
           <t>0.0</t>
+        </is>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>oui</t>
         </is>
       </c>
     </row>
@@ -8064,6 +9006,16 @@
           <t>49.7</t>
         </is>
       </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -8147,6 +9099,16 @@
           <t>63.0</t>
         </is>
       </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -8226,6 +9188,16 @@
           <t>49.7</t>
         </is>
       </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -8305,6 +9277,16 @@
           <t>49.7</t>
         </is>
       </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -8384,6 +9366,16 @@
           <t>49.7</t>
         </is>
       </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -8467,6 +9459,16 @@
           <t>49.7</t>
         </is>
       </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -8550,6 +9552,16 @@
           <t>81.0</t>
         </is>
       </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -8633,6 +9645,16 @@
           <t>49.7</t>
         </is>
       </c>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -8716,6 +9738,16 @@
           <t>49.7</t>
         </is>
       </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -8795,6 +9827,16 @@
           <t>49.7</t>
         </is>
       </c>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -8878,6 +9920,16 @@
           <t>49.7</t>
         </is>
       </c>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -8961,6 +10013,16 @@
           <t>49.7</t>
         </is>
       </c>
+      <c r="R106" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -9040,6 +10102,16 @@
           <t>0.0</t>
         </is>
       </c>
+      <c r="R107" t="inlineStr">
+        <is>
+          <t>association/fédération (bénévole)</t>
+        </is>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -9119,6 +10191,16 @@
           <t>0.0</t>
         </is>
       </c>
+      <c r="R108" t="inlineStr">
+        <is>
+          <t>association/fédération (bénévole)</t>
+        </is>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -9198,6 +10280,16 @@
           <t>0.0</t>
         </is>
       </c>
+      <c r="R109" t="inlineStr">
+        <is>
+          <t>association/fédération (bénévole)</t>
+        </is>
+      </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -9277,6 +10369,16 @@
           <t>0.0</t>
         </is>
       </c>
+      <c r="R110" t="inlineStr">
+        <is>
+          <t>association/fédération (bénévole)</t>
+        </is>
+      </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -9356,6 +10458,16 @@
           <t>0.0</t>
         </is>
       </c>
+      <c r="R111" t="inlineStr">
+        <is>
+          <t>association/fédération (bénévole)</t>
+        </is>
+      </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -9435,6 +10547,16 @@
           <t>0.0</t>
         </is>
       </c>
+      <c r="R112" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -9512,6 +10634,16 @@
       <c r="Q113" t="inlineStr">
         <is>
           <t>0.0</t>
+        </is>
+      </c>
+      <c r="R113" t="inlineStr">
+        <is>
+          <t>association/fédération (bénévole)</t>
+        </is>
+      </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
         </is>
       </c>
     </row>
@@ -9589,6 +10721,16 @@
           <t>18.9</t>
         </is>
       </c>
+      <c r="R114" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -9668,6 +10810,16 @@
           <t>0.0</t>
         </is>
       </c>
+      <c r="R115" t="inlineStr">
+        <is>
+          <t>grande entreprise (&gt;100)</t>
+        </is>
+      </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -9743,6 +10895,16 @@
           <t>0.0</t>
         </is>
       </c>
+      <c r="R116" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -9822,6 +10984,16 @@
           <t>14.7</t>
         </is>
       </c>
+      <c r="R117" t="inlineStr">
+        <is>
+          <t>grande entreprise (&gt;100)</t>
+        </is>
+      </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -9901,6 +11073,16 @@
           <t>14.7</t>
         </is>
       </c>
+      <c r="R118" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -9980,6 +11162,16 @@
           <t>12.2</t>
         </is>
       </c>
+      <c r="R119" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -10055,6 +11247,16 @@
           <t>0.0</t>
         </is>
       </c>
+      <c r="R120" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -10130,6 +11332,16 @@
           <t>0.0</t>
         </is>
       </c>
+      <c r="R121" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -10203,6 +11415,16 @@
       <c r="Q122" t="inlineStr">
         <is>
           <t>0.0</t>
+        </is>
+      </c>
+      <c r="R122" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>oui</t>
         </is>
       </c>
     </row>
@@ -10276,6 +11498,16 @@
           <t>0.0</t>
         </is>
       </c>
+      <c r="R123" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -10355,6 +11587,16 @@
           <t>0.0</t>
         </is>
       </c>
+      <c r="R124" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -10434,6 +11676,16 @@
           <t>0.0</t>
         </is>
       </c>
+      <c r="R125" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -10513,6 +11765,16 @@
           <t>27.6</t>
         </is>
       </c>
+      <c r="R126" t="inlineStr">
+        <is>
+          <t>association/fédération (bénévole)</t>
+        </is>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -10592,6 +11854,16 @@
           <t>49.7</t>
         </is>
       </c>
+      <c r="R127" t="inlineStr">
+        <is>
+          <t>association/fédération (bénévole)</t>
+        </is>
+      </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -10671,6 +11943,16 @@
           <t>49.7</t>
         </is>
       </c>
+      <c r="R128" t="inlineStr">
+        <is>
+          <t>association/fédération (bénévole)</t>
+        </is>
+      </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -10750,6 +12032,16 @@
           <t>27.6</t>
         </is>
       </c>
+      <c r="R129" t="inlineStr">
+        <is>
+          <t>association/fédération (bénévole)</t>
+        </is>
+      </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -10829,6 +12121,16 @@
           <t>27.6</t>
         </is>
       </c>
+      <c r="R130" t="inlineStr">
+        <is>
+          <t>association/fédération (bénévole)</t>
+        </is>
+      </c>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -10908,6 +12210,16 @@
           <t>27.6</t>
         </is>
       </c>
+      <c r="R131" t="inlineStr">
+        <is>
+          <t>association/fédération (bénévole)</t>
+        </is>
+      </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -10987,6 +12299,16 @@
           <t>27.6</t>
         </is>
       </c>
+      <c r="R132" t="inlineStr">
+        <is>
+          <t>association/fédération (bénévole)</t>
+        </is>
+      </c>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -11066,6 +12388,16 @@
           <t>27.6</t>
         </is>
       </c>
+      <c r="R133" t="inlineStr">
+        <is>
+          <t>association/fédération (bénévole)</t>
+        </is>
+      </c>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -11145,6 +12477,16 @@
           <t>27.6</t>
         </is>
       </c>
+      <c r="R134" t="inlineStr">
+        <is>
+          <t>association/fédération (bénévole)</t>
+        </is>
+      </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -11224,6 +12566,16 @@
           <t>49.7</t>
         </is>
       </c>
+      <c r="R135" t="inlineStr">
+        <is>
+          <t>association/fédération (bénévole)</t>
+        </is>
+      </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -11303,6 +12655,16 @@
           <t>27.6</t>
         </is>
       </c>
+      <c r="R136" t="inlineStr">
+        <is>
+          <t>association/fédération (bénévole)</t>
+        </is>
+      </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -11382,6 +12744,16 @@
           <t>27.6</t>
         </is>
       </c>
+      <c r="R137" t="inlineStr">
+        <is>
+          <t>association/fédération (bénévole)</t>
+        </is>
+      </c>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -11461,6 +12833,16 @@
           <t>49.7</t>
         </is>
       </c>
+      <c r="R138" t="inlineStr">
+        <is>
+          <t>association/fédération (bénévole)</t>
+        </is>
+      </c>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -11540,6 +12922,16 @@
           <t>49.7</t>
         </is>
       </c>
+      <c r="R139" t="inlineStr">
+        <is>
+          <t>association/fédération (bénévole)</t>
+        </is>
+      </c>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -11619,6 +13011,16 @@
           <t>49.7</t>
         </is>
       </c>
+      <c r="R140" t="inlineStr">
+        <is>
+          <t>association/fédération (bénévole)</t>
+        </is>
+      </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -11698,6 +13100,16 @@
           <t>27.6</t>
         </is>
       </c>
+      <c r="R141" t="inlineStr">
+        <is>
+          <t>association/fédération (bénévole)</t>
+        </is>
+      </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -11773,6 +13185,16 @@
           <t>0.0</t>
         </is>
       </c>
+      <c r="R142" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -11848,6 +13270,16 @@
           <t>0.0</t>
         </is>
       </c>
+      <c r="R143" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -11923,6 +13355,16 @@
           <t>0.0</t>
         </is>
       </c>
+      <c r="R144" t="inlineStr">
+        <is>
+          <t>association/fédération (bénévole)</t>
+        </is>
+      </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -11998,6 +13440,16 @@
           <t>0.0</t>
         </is>
       </c>
+      <c r="R145" t="inlineStr">
+        <is>
+          <t>association/fédération (bénévole)</t>
+        </is>
+      </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -12073,6 +13525,16 @@
           <t>0.0</t>
         </is>
       </c>
+      <c r="R146" t="inlineStr">
+        <is>
+          <t>association/fédération (bénévole)</t>
+        </is>
+      </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -12148,6 +13610,16 @@
           <t>0.0</t>
         </is>
       </c>
+      <c r="R147" t="inlineStr">
+        <is>
+          <t>association/fédération (bénévole)</t>
+        </is>
+      </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -12227,6 +13699,16 @@
           <t>17.5</t>
         </is>
       </c>
+      <c r="R148" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -12306,6 +13788,16 @@
           <t>49.7</t>
         </is>
       </c>
+      <c r="R149" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -12385,6 +13877,16 @@
           <t>49.7</t>
         </is>
       </c>
+      <c r="R150" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -12464,6 +13966,16 @@
           <t>49.7</t>
         </is>
       </c>
+      <c r="R151" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -12541,6 +14053,16 @@
       <c r="Q152" t="inlineStr">
         <is>
           <t>49.7</t>
+        </is>
+      </c>
+      <c r="R152" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>oui</t>
         </is>
       </c>
     </row>
@@ -12614,6 +14136,16 @@
           <t>0.0</t>
         </is>
       </c>
+      <c r="R153" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -12689,6 +14221,16 @@
           <t>0.0</t>
         </is>
       </c>
+      <c r="R154" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -12764,6 +14306,16 @@
           <t>0.0</t>
         </is>
       </c>
+      <c r="R155" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -12839,6 +14391,16 @@
           <t>0.0</t>
         </is>
       </c>
+      <c r="R156" t="inlineStr">
+        <is>
+          <t>grande entreprise (&gt;100)</t>
+        </is>
+      </c>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -12914,6 +14476,16 @@
           <t>0.0</t>
         </is>
       </c>
+      <c r="R157" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -12993,6 +14565,16 @@
           <t>38.2</t>
         </is>
       </c>
+      <c r="R158" t="inlineStr">
+        <is>
+          <t>grande fortune / célébrité</t>
+        </is>
+      </c>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -13072,6 +14654,16 @@
           <t>35.0</t>
         </is>
       </c>
+      <c r="R159" t="inlineStr">
+        <is>
+          <t>association/fédération (bénévole)</t>
+        </is>
+      </c>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -13151,6 +14743,16 @@
           <t>49.7</t>
         </is>
       </c>
+      <c r="R160" t="inlineStr">
+        <is>
+          <t>association/fédération (bénévole)</t>
+        </is>
+      </c>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -13230,6 +14832,16 @@
           <t>25.2</t>
         </is>
       </c>
+      <c r="R161" t="inlineStr">
+        <is>
+          <t>association/fédération (bénévole)</t>
+        </is>
+      </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -13309,6 +14921,16 @@
           <t>49.7</t>
         </is>
       </c>
+      <c r="R162" t="inlineStr">
+        <is>
+          <t>association/fédération (bénévole)</t>
+        </is>
+      </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -13388,6 +15010,16 @@
           <t>49.7</t>
         </is>
       </c>
+      <c r="R163" t="inlineStr">
+        <is>
+          <t>association/fédération (bénévole)</t>
+        </is>
+      </c>
+      <c r="S163" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -13467,6 +15099,16 @@
           <t>49.7</t>
         </is>
       </c>
+      <c r="R164" t="inlineStr">
+        <is>
+          <t>association/fédération (bénévole)</t>
+        </is>
+      </c>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -13546,6 +15188,16 @@
           <t>49.7</t>
         </is>
       </c>
+      <c r="R165" t="inlineStr">
+        <is>
+          <t>association/fédération (bénévole)</t>
+        </is>
+      </c>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -13625,6 +15277,16 @@
           <t>49.7</t>
         </is>
       </c>
+      <c r="R166" t="inlineStr">
+        <is>
+          <t>association/fédération (bénévole)</t>
+        </is>
+      </c>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -13704,6 +15366,16 @@
           <t>27.6</t>
         </is>
       </c>
+      <c r="R167" t="inlineStr">
+        <is>
+          <t>association/fédération (bénévole)</t>
+        </is>
+      </c>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -13783,6 +15455,16 @@
           <t>27.6</t>
         </is>
       </c>
+      <c r="R168" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -13862,6 +15544,16 @@
           <t>63.0</t>
         </is>
       </c>
+      <c r="R169" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -13941,6 +15633,16 @@
           <t>35.0</t>
         </is>
       </c>
+      <c r="R170" t="inlineStr">
+        <is>
+          <t>association/fédération (bénévole)</t>
+        </is>
+      </c>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -14020,6 +15722,16 @@
           <t>49.0</t>
         </is>
       </c>
+      <c r="R171" t="inlineStr">
+        <is>
+          <t>association/fédération (bénévole)</t>
+        </is>
+      </c>
+      <c r="S171" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -14099,6 +15811,16 @@
           <t>49.0</t>
         </is>
       </c>
+      <c r="R172" t="inlineStr">
+        <is>
+          <t>association/fédération (bénévole)</t>
+        </is>
+      </c>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -14178,6 +15900,16 @@
           <t>49.0</t>
         </is>
       </c>
+      <c r="R173" t="inlineStr">
+        <is>
+          <t>association/fédération (bénévole)</t>
+        </is>
+      </c>
+      <c r="S173" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -14257,6 +15989,16 @@
           <t>49.0</t>
         </is>
       </c>
+      <c r="R174" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S174" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -14336,6 +16078,16 @@
           <t>49.0</t>
         </is>
       </c>
+      <c r="R175" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S175" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -14411,6 +16163,16 @@
           <t>0.0</t>
         </is>
       </c>
+      <c r="R176" t="inlineStr">
+        <is>
+          <t>association/fédération (bénévole)</t>
+        </is>
+      </c>
+      <c r="S176" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -14486,6 +16248,16 @@
           <t>0.0</t>
         </is>
       </c>
+      <c r="R177" t="inlineStr">
+        <is>
+          <t>association/fédération (bénévole)</t>
+        </is>
+      </c>
+      <c r="S177" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -14561,6 +16333,16 @@
           <t>0.0</t>
         </is>
       </c>
+      <c r="R178" t="inlineStr">
+        <is>
+          <t>association/fédération (bénévole)</t>
+        </is>
+      </c>
+      <c r="S178" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -14636,6 +16418,16 @@
           <t>0.0</t>
         </is>
       </c>
+      <c r="R179" t="inlineStr">
+        <is>
+          <t>association/fédération (bénévole)</t>
+        </is>
+      </c>
+      <c r="S179" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -14711,6 +16503,16 @@
           <t>0.0</t>
         </is>
       </c>
+      <c r="R180" t="inlineStr">
+        <is>
+          <t>association/fédération (bénévole)</t>
+        </is>
+      </c>
+      <c r="S180" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -14786,6 +16588,16 @@
           <t>0.0</t>
         </is>
       </c>
+      <c r="R181" t="inlineStr">
+        <is>
+          <t>association/fédération (bénévole)</t>
+        </is>
+      </c>
+      <c r="S181" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -14861,6 +16673,16 @@
           <t>0.0</t>
         </is>
       </c>
+      <c r="R182" t="inlineStr">
+        <is>
+          <t>association/fédération (bénévole)</t>
+        </is>
+      </c>
+      <c r="S182" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -14940,6 +16762,16 @@
           <t>0.0</t>
         </is>
       </c>
+      <c r="R183" t="inlineStr">
+        <is>
+          <t>association/fédération (bénévole)</t>
+        </is>
+      </c>
+      <c r="S183" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -15019,6 +16851,16 @@
           <t>0.0</t>
         </is>
       </c>
+      <c r="R184" t="inlineStr">
+        <is>
+          <t>association/fédération (bénévole)</t>
+        </is>
+      </c>
+      <c r="S184" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -15098,6 +16940,16 @@
           <t>27.6</t>
         </is>
       </c>
+      <c r="R185" t="inlineStr">
+        <is>
+          <t>association/fédération (bénévole)</t>
+        </is>
+      </c>
+      <c r="S185" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -15177,6 +17029,16 @@
           <t>49.7</t>
         </is>
       </c>
+      <c r="R186" t="inlineStr">
+        <is>
+          <t>association/fédération (bénévole)</t>
+        </is>
+      </c>
+      <c r="S186" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -15260,6 +17122,16 @@
           <t>49.7</t>
         </is>
       </c>
+      <c r="R187" t="inlineStr">
+        <is>
+          <t>association/fédération (bénévole)</t>
+        </is>
+      </c>
+      <c r="S187" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -15339,6 +17211,16 @@
           <t>49.7</t>
         </is>
       </c>
+      <c r="R188" t="inlineStr">
+        <is>
+          <t>association/fédération (bénévole)</t>
+        </is>
+      </c>
+      <c r="S188" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -15418,6 +17300,16 @@
           <t>49.7</t>
         </is>
       </c>
+      <c r="R189" t="inlineStr">
+        <is>
+          <t>association/fédération (bénévole)</t>
+        </is>
+      </c>
+      <c r="S189" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -15497,6 +17389,16 @@
           <t>49.7</t>
         </is>
       </c>
+      <c r="R190" t="inlineStr">
+        <is>
+          <t>association/fédération (bénévole)</t>
+        </is>
+      </c>
+      <c r="S190" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -15576,6 +17478,16 @@
           <t>49.7</t>
         </is>
       </c>
+      <c r="R191" t="inlineStr">
+        <is>
+          <t>association/fédération (bénévole)</t>
+        </is>
+      </c>
+      <c r="S191" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -15655,6 +17567,16 @@
           <t>49.7</t>
         </is>
       </c>
+      <c r="R192" t="inlineStr">
+        <is>
+          <t>association/fédération (bénévole)</t>
+        </is>
+      </c>
+      <c r="S192" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -15734,6 +17656,16 @@
           <t>49.7</t>
         </is>
       </c>
+      <c r="R193" t="inlineStr">
+        <is>
+          <t>association/fédération (bénévole)</t>
+        </is>
+      </c>
+      <c r="S193" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -15813,6 +17745,16 @@
           <t>27.6</t>
         </is>
       </c>
+      <c r="R194" t="inlineStr">
+        <is>
+          <t>association/fédération (bénévole)</t>
+        </is>
+      </c>
+      <c r="S194" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -15892,6 +17834,16 @@
           <t>27.6</t>
         </is>
       </c>
+      <c r="R195" t="inlineStr">
+        <is>
+          <t>association/fédération (bénévole)</t>
+        </is>
+      </c>
+      <c r="S195" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -15971,6 +17923,16 @@
           <t>27.6</t>
         </is>
       </c>
+      <c r="R196" t="inlineStr">
+        <is>
+          <t>association/fédération (bénévole)</t>
+        </is>
+      </c>
+      <c r="S196" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -16050,6 +18012,16 @@
           <t>27.6</t>
         </is>
       </c>
+      <c r="R197" t="inlineStr">
+        <is>
+          <t>association/fédération (bénévole)</t>
+        </is>
+      </c>
+      <c r="S197" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -16129,6 +18101,16 @@
           <t>49.7</t>
         </is>
       </c>
+      <c r="R198" t="inlineStr">
+        <is>
+          <t>association/fédération (bénévole)</t>
+        </is>
+      </c>
+      <c r="S198" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -16208,6 +18190,16 @@
           <t>49.7</t>
         </is>
       </c>
+      <c r="R199" t="inlineStr">
+        <is>
+          <t>association/fédération (bénévole)</t>
+        </is>
+      </c>
+      <c r="S199" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -16287,6 +18279,16 @@
           <t>49.7</t>
         </is>
       </c>
+      <c r="R200" t="inlineStr">
+        <is>
+          <t>association/fédération (bénévole)</t>
+        </is>
+      </c>
+      <c r="S200" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -16366,6 +18368,16 @@
           <t>49.7</t>
         </is>
       </c>
+      <c r="R201" t="inlineStr">
+        <is>
+          <t>association/fédération (bénévole)</t>
+        </is>
+      </c>
+      <c r="S201" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -16445,6 +18457,16 @@
           <t>49.7</t>
         </is>
       </c>
+      <c r="R202" t="inlineStr">
+        <is>
+          <t>association/fédération (bénévole)</t>
+        </is>
+      </c>
+      <c r="S202" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -16524,6 +18546,16 @@
           <t>49.7</t>
         </is>
       </c>
+      <c r="R203" t="inlineStr">
+        <is>
+          <t>association/fédération (bénévole)</t>
+        </is>
+      </c>
+      <c r="S203" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -16603,6 +18635,16 @@
           <t>49.7</t>
         </is>
       </c>
+      <c r="R204" t="inlineStr">
+        <is>
+          <t>association/fédération (bénévole)</t>
+        </is>
+      </c>
+      <c r="S204" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -16682,6 +18724,16 @@
           <t>49.7</t>
         </is>
       </c>
+      <c r="R205" t="inlineStr">
+        <is>
+          <t>association/fédération (bénévole)</t>
+        </is>
+      </c>
+      <c r="S205" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -16761,6 +18813,16 @@
           <t>49.7</t>
         </is>
       </c>
+      <c r="R206" t="inlineStr">
+        <is>
+          <t>association/fédération (bénévole)</t>
+        </is>
+      </c>
+      <c r="S206" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -16840,6 +18902,16 @@
           <t>49.7</t>
         </is>
       </c>
+      <c r="R207" t="inlineStr">
+        <is>
+          <t>association/fédération (bénévole)</t>
+        </is>
+      </c>
+      <c r="S207" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -16919,6 +18991,16 @@
           <t>49.7</t>
         </is>
       </c>
+      <c r="R208" t="inlineStr">
+        <is>
+          <t>association/fédération (bénévole)</t>
+        </is>
+      </c>
+      <c r="S208" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -16998,6 +19080,16 @@
           <t>49.7</t>
         </is>
       </c>
+      <c r="R209" t="inlineStr">
+        <is>
+          <t>association/fédération (bénévole)</t>
+        </is>
+      </c>
+      <c r="S209" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -17077,6 +19169,16 @@
           <t>49.7</t>
         </is>
       </c>
+      <c r="R210" t="inlineStr">
+        <is>
+          <t>association/fédération (bénévole)</t>
+        </is>
+      </c>
+      <c r="S210" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -17156,6 +19258,16 @@
           <t>49.7</t>
         </is>
       </c>
+      <c r="R211" t="inlineStr">
+        <is>
+          <t>association/fédération (bénévole)</t>
+        </is>
+      </c>
+      <c r="S211" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -17235,6 +19347,16 @@
           <t>49.7</t>
         </is>
       </c>
+      <c r="R212" t="inlineStr">
+        <is>
+          <t>association/fédération (bénévole)</t>
+        </is>
+      </c>
+      <c r="S212" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -17314,6 +19436,16 @@
           <t>49.7</t>
         </is>
       </c>
+      <c r="R213" t="inlineStr">
+        <is>
+          <t>association/fédération (bénévole)</t>
+        </is>
+      </c>
+      <c r="S213" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -17393,6 +19525,16 @@
           <t>49.7</t>
         </is>
       </c>
+      <c r="R214" t="inlineStr">
+        <is>
+          <t>association/fédération (bénévole)</t>
+        </is>
+      </c>
+      <c r="S214" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -17472,6 +19614,16 @@
           <t>49.7</t>
         </is>
       </c>
+      <c r="R215" t="inlineStr">
+        <is>
+          <t>association/fédération (bénévole)</t>
+        </is>
+      </c>
+      <c r="S215" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -17551,6 +19703,16 @@
           <t>49.7</t>
         </is>
       </c>
+      <c r="R216" t="inlineStr">
+        <is>
+          <t>association/fédération (bénévole)</t>
+        </is>
+      </c>
+      <c r="S216" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -17630,6 +19792,16 @@
           <t>49.7</t>
         </is>
       </c>
+      <c r="R217" t="inlineStr">
+        <is>
+          <t>association/fédération (bénévole)</t>
+        </is>
+      </c>
+      <c r="S217" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -17709,6 +19881,16 @@
           <t>49.7</t>
         </is>
       </c>
+      <c r="R218" t="inlineStr">
+        <is>
+          <t>association/fédération (bénévole)</t>
+        </is>
+      </c>
+      <c r="S218" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -17788,6 +19970,16 @@
           <t>49.7</t>
         </is>
       </c>
+      <c r="R219" t="inlineStr">
+        <is>
+          <t>association/fédération (bénévole)</t>
+        </is>
+      </c>
+      <c r="S219" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -17867,6 +20059,16 @@
           <t>49.7</t>
         </is>
       </c>
+      <c r="R220" t="inlineStr">
+        <is>
+          <t>association/fédération (bénévole)</t>
+        </is>
+      </c>
+      <c r="S220" t="inlineStr">
+        <is>
+          <t>a_confirmer</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -17944,6 +20146,696 @@
       <c r="Q221" t="inlineStr">
         <is>
           <t>49.7</t>
+        </is>
+      </c>
+      <c r="R221" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S221" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>B-profil LinkedIn à qualifier</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Gérald Brault</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Dirigeant (distributeur de produits équins)</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>Distribution équine (TPE)</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr"/>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/g%C3%A9rald-brault-07161a97</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr"/>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>Cavalier pratiquant affiché sur le profil (dirigeant de TPE)</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>Profil « Cavalier, distributeur de produits equins » — cavalier pratiquant (NB: déjà dans la filière équine)</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/g%C3%A9rald-brault-07161a97</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t>aucun</t>
+        </is>
+      </c>
+      <c r="O222" t="inlineStr"/>
+      <c r="P222" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q222" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R222" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S222" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>B-profil LinkedIn à qualifier</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Lamia Moraine</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Cofondatrice &amp; Directrice Générale</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>Inovelite</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr"/>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/lamia-moraine-inovelite</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr"/>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>Indice équestre détecté via requête Google croisée (à confirmer sur le profil)</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>Profil remonté sur requête « cavalière » + cofondatrice/DG (PME)</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/lamia-moraine-inovelite</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>aucun</t>
+        </is>
+      </c>
+      <c r="O223" t="inlineStr"/>
+      <c r="P223" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q223" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R223" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S223" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>B-profil LinkedIn à qualifier</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Isabelle Delannoy</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Présidente</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>L'Entreprise Symbiotique</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr"/>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/isabelle-delannoy-8337225</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr"/>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>Indice équestre détecté via requête Google croisée (à confirmer sur le profil)</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>Profil remonté sur requête « cavalière » + présidente (petite structure)</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/isabelle-delannoy-8337225</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>aucun</t>
+        </is>
+      </c>
+      <c r="O224" t="inlineStr"/>
+      <c r="P224" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q224" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R224" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S224" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>B-profil LinkedIn à qualifier</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Eve Pauvert</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Dirigeante</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Facilis.fr (TPE/PME, Alsace)</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr"/>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/eve-pauvert-dirigeante-facilis-cse-tpe-pme-alsace-grandest</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr"/>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>Indice équestre détecté via requête Google croisée (à confirmer sur le profil)</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>Profil remonté sur requête « dirigeante » TPE/PME + « cavalière »/concours</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/eve-pauvert-dirigeante-facilis-cse-tpe-pme-alsace-grandest</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>aucun</t>
+        </is>
+      </c>
+      <c r="O225" t="inlineStr"/>
+      <c r="P225" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q225" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R225" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S225" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>B-profil LinkedIn à qualifier</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Vanessa Logerais</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Fondatrice / dirigeante</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>Parangone (agence)</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr"/>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/vanessa-logerais-parangone</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr"/>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>Indice équestre détecté via requête Google croisée (à confirmer sur le profil)</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>Profil remonté sur requête « dirigeante » PME + « cavalière »</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/vanessa-logerais-parangone</t>
+        </is>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>aucun</t>
+        </is>
+      </c>
+      <c r="O226" t="inlineStr"/>
+      <c r="P226" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q226" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R226" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S226" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>B-profil LinkedIn à qualifier</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Rafaëlle Rivier</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Présidente</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>MOMA Consulting</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr"/>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/rafaelle-rivier</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr"/>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>Indice équestre détecté via requête Google croisée (à confirmer sur le profil)</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>Profil remonté sur requête « dirigeante » + « cavalière »/concours (conseil, PME)</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/rafaelle-rivier</t>
+        </is>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>aucun</t>
+        </is>
+      </c>
+      <c r="O227" t="inlineStr"/>
+      <c r="P227" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q227" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R227" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S227" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>B-profil LinkedIn à qualifier</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Pauline Laigneau</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Fondatrice</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Gemmyo / Demian Education</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr"/>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/pauline-laigneau</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr"/>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>Indice équestre détecté via requête Google croisée (à confirmer sur le profil)</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>Profil remonté sur requête « cavalière » + fondatrice (à confirmer; taille Gemmyo à vérifier)</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/pauline-laigneau</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>aucun</t>
+        </is>
+      </c>
+      <c r="O228" t="inlineStr"/>
+      <c r="P228" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q228" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R228" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S228" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>B-profil LinkedIn à qualifier</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Caroline Clavel</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Gérante</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>Écurie (TPE)</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr"/>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/caroline-clavel-40ba79197</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr"/>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>Cavalière pratiquante affichée sur le profil (gérante de TPE)</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>Profil « Gérante - Cavalière » — cavalière pratiquante (NB: gère une écurie, filière équine)</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/caroline-clavel-40ba79197</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>aucun</t>
+        </is>
+      </c>
+      <c r="O229" t="inlineStr"/>
+      <c r="P229" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q229" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R229" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S229" t="inlineStr">
+        <is>
+          <t>oui</t>
         </is>
       </c>
     </row>

--- a/data/prospects.xlsx
+++ b/data/prospects.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Prospects" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S229"/>
+  <dimension ref="A1:S232"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -20839,6 +20839,273 @@
         </is>
       </c>
     </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>B-profil LinkedIn à qualifier</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Marie Dauxerre</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Gérante fondatrice</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>Abeille Informatique (PME)</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr"/>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/marie-dauxerre-4298b858</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr"/>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>Indice équestre détecté via requête Google croisée (à confirmer sur le profil)</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>Profil « gérante fondatrice » remonté sur requête équitation/cheval + PME</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/marie-dauxerre-4298b858</t>
+        </is>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>incertain</t>
+        </is>
+      </c>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>affinite_cheval</t>
+        </is>
+      </c>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>mention équestre générique</t>
+        </is>
+      </c>
+      <c r="P230" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="Q230" t="inlineStr">
+        <is>
+          <t>28.4</t>
+        </is>
+      </c>
+      <c r="R230" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S230" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>B-profil LinkedIn à qualifier</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Joëlle Daumas-Guirado</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>CEO (créatrice de crampons pneus)</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>UGIGRIP (PME industrielle)</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr"/>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/jo%C3%ABlle-daumas-guirado/en</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr"/>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>Indice équestre détecté via requête Google croisée (à confirmer sur le profil)</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>Profil CEO PME remonté sur requête « cavalier/équitation » + indépendant</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/jo%C3%ABlle-daumas-guirado/en</t>
+        </is>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>incertain</t>
+        </is>
+      </c>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>affinite_cheval</t>
+        </is>
+      </c>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>mention équestre générique</t>
+        </is>
+      </c>
+      <c r="P231" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="Q231" t="inlineStr">
+        <is>
+          <t>28.4</t>
+        </is>
+      </c>
+      <c r="R231" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S231" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>B-profil LinkedIn à qualifier</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Samuel Usureau</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Directeur Commercial</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>JDA Dijon</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr"/>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/samuel-usureau-88b293139</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr"/>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>Indice équestre détecté via requête Google croisée (à confirmer sur le profil)</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>Profil remonté sur requête « directeur » + dressage/saut d'obstacles amateur</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/samuel-usureau-88b293139</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>cavalier_pratiquant</t>
+        </is>
+      </c>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>dressage</t>
+        </is>
+      </c>
+      <c r="P232" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="Q232" t="inlineStr">
+        <is>
+          <t>49.0</t>
+        </is>
+      </c>
+      <c r="R232" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S232" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
